--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="current" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="history" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="current" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="history" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,10 +477,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6988118485.783855</v>
+        <v>6989302482.06953</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>37.55531979</v>
+        <v>37.55863602</v>
       </c>
       <c r="E2" t="n">
         <v>1219</v>
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3956880301.391687</v>
+        <v>3956961085.227087</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.26493782</v>
+        <v>21.26364705</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2403369254.308203</v>
+        <v>2403369332.569065</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12.91610912</v>
+        <v>12.91506187</v>
       </c>
       <c r="E4" t="n">
         <v>299</v>
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2194396498.034477</v>
+        <v>2194418461.59156</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>11.79305451</v>
+        <v>11.79221596</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1966208914.042868</v>
+        <v>1966444831.173599</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.56673619</v>
+        <v>10.56714684</v>
       </c>
       <c r="E6" t="n">
         <v>133</v>
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>644592144.2337281</v>
+        <v>886410189.0294122</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.4641462</v>
+        <v>4.76333049</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -599,17 +599,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>278066655.1681771</v>
+        <v>175900648.6948009</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.4943768</v>
+        <v>0.94524288</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -620,17 +620,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>175900648.6948009</v>
+        <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.9453195599999999</v>
+        <v>0.19471888</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2194396498.034477</v>
+        <v>2194418461.59156</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>11.79305451</v>
+        <v>11.79221596</v>
       </c>
       <c r="E2" t="n">
         <v>48</v>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2403369254.308203</v>
+        <v>2403369332.569065</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>12.91610912</v>
+        <v>12.91506187</v>
       </c>
       <c r="E3" t="n">
         <v>299</v>
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>644592144.2337281</v>
+        <v>886410189.0294122</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3.4641462</v>
+        <v>4.76333049</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1966208914.042868</v>
+        <v>1966444831.173599</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>10.56673619</v>
+        <v>10.56714684</v>
       </c>
       <c r="E5" t="n">
         <v>133</v>
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3956880301.391687</v>
+        <v>3956961085.227087</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>21.26493782</v>
+        <v>21.26364705</v>
       </c>
       <c r="E6" t="n">
         <v>228</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6988118485.783855</v>
+        <v>6989302482.06953</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>37.55531979</v>
+        <v>37.55863602</v>
       </c>
       <c r="E7" t="n">
         <v>1219</v>
@@ -822,7 +822,7 @@
         <v>175900648.6948009</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.9453195599999999</v>
+        <v>0.94524288</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>278066655.1681771</v>
+        <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1.4943768</v>
+        <v>0.19471888</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -477,10 +477,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6989302482.06953</v>
+        <v>6989294430.159245</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>37.55863602</v>
+        <v>37.55860308</v>
       </c>
       <c r="E2" t="n">
         <v>1219</v>
@@ -501,7 +501,7 @@
         <v>3956961085.227087</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.26364705</v>
+        <v>21.26365291</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -522,7 +522,7 @@
         <v>2403369332.569065</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12.91506187</v>
+        <v>12.91506542</v>
       </c>
       <c r="E4" t="n">
         <v>299</v>
@@ -543,7 +543,7 @@
         <v>2194418461.59156</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>11.79221596</v>
+        <v>11.7922192</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1966444831.173599</v>
+        <v>1966445348.300837</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.56714684</v>
+        <v>10.56715253</v>
       </c>
       <c r="E6" t="n">
         <v>133</v>
@@ -585,7 +585,7 @@
         <v>886410189.0294122</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.76333049</v>
+        <v>4.76333181</v>
       </c>
       <c r="E7" t="n">
         <v>45</v>
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175900648.6948009</v>
+        <v>175903061.8948109</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.94524288</v>
+        <v>0.94525611</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -627,7 +627,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.19471888</v>
+        <v>0.19471894</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -696,7 +696,7 @@
         <v>2194418461.59156</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>11.79221596</v>
+        <v>11.7922192</v>
       </c>
       <c r="E2" t="n">
         <v>48</v>
@@ -717,7 +717,7 @@
         <v>2403369332.569065</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>12.91506187</v>
+        <v>12.91506542</v>
       </c>
       <c r="E3" t="n">
         <v>299</v>
@@ -738,7 +738,7 @@
         <v>886410189.0294122</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4.76333049</v>
+        <v>4.76333181</v>
       </c>
       <c r="E4" t="n">
         <v>45</v>
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1966444831.173599</v>
+        <v>1966445348.300837</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>10.56714684</v>
+        <v>10.56715253</v>
       </c>
       <c r="E5" t="n">
         <v>133</v>
@@ -780,7 +780,7 @@
         <v>3956961085.227087</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>21.26364705</v>
+        <v>21.26365291</v>
       </c>
       <c r="E6" t="n">
         <v>228</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6989302482.06953</v>
+        <v>6989294430.159245</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>37.55863602</v>
+        <v>37.55860308</v>
       </c>
       <c r="E7" t="n">
         <v>1219</v>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175900648.6948009</v>
+        <v>175903061.8948109</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.94524288</v>
+        <v>0.94525611</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -843,7 +843,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.19471888</v>
+        <v>0.19471894</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -477,10 +477,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6989294430.159245</v>
+        <v>6989362721.120035</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>37.55860308</v>
+        <v>37.56122812</v>
       </c>
       <c r="E2" t="n">
         <v>1219</v>
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3956961085.227087</v>
+        <v>3956941070.671131</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.26365291</v>
+        <v>21.26482373</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2403369332.569065</v>
+        <v>2403368774.979801</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12.91506542</v>
+        <v>12.91583889</v>
       </c>
       <c r="E4" t="n">
         <v>299</v>
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2194418461.59156</v>
+        <v>2194416383.782233</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>11.7922192</v>
+        <v>11.79291699</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1966445348.300837</v>
+        <v>1965282807.524859</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.56715253</v>
+        <v>10.56154027</v>
       </c>
       <c r="E6" t="n">
         <v>133</v>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>886410189.0294122</v>
+        <v>886408371.9442221</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.76333181</v>
+        <v>4.76360841</v>
       </c>
       <c r="E7" t="n">
         <v>45</v>
@@ -606,7 +606,7 @@
         <v>175903061.8948109</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.94525611</v>
+        <v>0.94531294</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -627,7 +627,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.19471894</v>
+        <v>0.19473064</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2194418461.59156</v>
+        <v>2194416383.782233</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>11.7922192</v>
+        <v>11.79291699</v>
       </c>
       <c r="E2" t="n">
         <v>48</v>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2403369332.569065</v>
+        <v>2403368774.979801</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>12.91506542</v>
+        <v>12.91583889</v>
       </c>
       <c r="E3" t="n">
         <v>299</v>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>886410189.0294122</v>
+        <v>886408371.9442221</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4.76333181</v>
+        <v>4.76360841</v>
       </c>
       <c r="E4" t="n">
         <v>45</v>
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1966445348.300837</v>
+        <v>1965282807.524859</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>10.56715253</v>
+        <v>10.56154027</v>
       </c>
       <c r="E5" t="n">
         <v>133</v>
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3956961085.227087</v>
+        <v>3956941070.671131</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>21.26365291</v>
+        <v>21.26482373</v>
       </c>
       <c r="E6" t="n">
         <v>228</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6989294430.159245</v>
+        <v>6989362721.120035</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>37.55860308</v>
+        <v>37.56122812</v>
       </c>
       <c r="E7" t="n">
         <v>1219</v>
@@ -822,7 +822,7 @@
         <v>175903061.8948109</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.94525611</v>
+        <v>0.94531294</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -843,7 +843,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.19471894</v>
+        <v>0.19473064</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="current" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="history" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="current" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="history" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +30,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +44,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002D5A87"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,13 +64,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -631,6 +642,27 @@
       </c>
       <c r="E9" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>18607918511.16997</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>2000</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="current" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="history" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="current" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="history" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,13 +488,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6989362721.120035</v>
+        <v>6914009797.573305</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>37.56122812</v>
+        <v>37.28749445</v>
       </c>
       <c r="E2" t="n">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="3">
@@ -509,13 +509,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3956941070.671131</v>
+        <v>3964094360.299066</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.26482373</v>
+        <v>21.37849826</v>
       </c>
       <c r="E3" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2403368774.979801</v>
+        <v>2401995105.256982</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12.91583889</v>
+        <v>12.95404285</v>
       </c>
       <c r="E4" t="n">
         <v>299</v>
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2194416383.782233</v>
+        <v>2195104278.93793</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>11.79291699</v>
+        <v>11.83827345</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1965282807.524859</v>
+        <v>1971001597.471919</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.56154027</v>
+        <v>10.62967992</v>
       </c>
       <c r="E6" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>886408371.9442221</v>
+        <v>884052468.7843171</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.76360841</v>
+        <v>4.7677256</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175903061.8948109</v>
+        <v>175943081.6987769</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.94531294</v>
+        <v>0.9488671400000001</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.19473064</v>
+        <v>0.19541833</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>18607918511.16997</v>
+        <v>18542436009.27517</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2194416383.782233</v>
+        <v>2195104278.93793</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>11.79291699</v>
+        <v>11.83827345</v>
       </c>
       <c r="E2" t="n">
         <v>48</v>
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2403368774.979801</v>
+        <v>2401995105.256982</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>12.91583889</v>
+        <v>12.95404285</v>
       </c>
       <c r="E3" t="n">
         <v>299</v>
@@ -767,13 +767,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>886408371.9442221</v>
+        <v>884052468.7843171</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4.76360841</v>
+        <v>4.7677256</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -788,13 +788,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1965282807.524859</v>
+        <v>1971001597.471919</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>10.56154027</v>
+        <v>10.62967992</v>
       </c>
       <c r="E5" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3956941070.671131</v>
+        <v>3964094360.299066</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>21.26482373</v>
+        <v>21.37849826</v>
       </c>
       <c r="E6" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6989362721.120035</v>
+        <v>6914009797.573305</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>37.56122812</v>
+        <v>37.28749445</v>
       </c>
       <c r="E7" t="n">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="8">
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175903061.8948109</v>
+        <v>175943081.6987769</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.94531294</v>
+        <v>0.9488671400000001</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -875,7 +875,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.19473064</v>
+        <v>0.19541833</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6914009797.573305</v>
+        <v>6492400775.188599</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>37.28749445</v>
+        <v>35.72800996</v>
       </c>
       <c r="E2" t="n">
-        <v>1218</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3964094360.299066</v>
+        <v>4008398749.148034</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.37849826</v>
+        <v>22.05842113</v>
       </c>
       <c r="E3" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2401995105.256982</v>
+        <v>2424619185.940132</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12.95404285</v>
+        <v>13.34280206</v>
       </c>
       <c r="E4" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2195104278.93793</v>
+        <v>2158273413.781404</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>11.83827345</v>
+        <v>11.8770878</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1971001597.471919</v>
+        <v>1992324194.81826</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.62967992</v>
+        <v>10.96386085</v>
       </c>
       <c r="E6" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>884052468.7843171</v>
+        <v>886313475.1740601</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.7677256</v>
+        <v>4.8774279</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175943081.6987769</v>
+        <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.9488671400000001</v>
+        <v>0.95298552</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.19541833</v>
+        <v>0.1994048</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>18542436009.27517</v>
+        <v>18171739156.51621</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -881,6 +881,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>2158273413.781404</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>11.8770878</v>
+      </c>
+      <c r="E10" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>2424619185.940132</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>13.34280206</v>
+      </c>
+      <c r="E11" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>886313475.1740601</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>4.8774279</v>
+      </c>
+      <c r="E12" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>1992324194.81826</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>10.96386085</v>
+      </c>
+      <c r="E13" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>4008398749.148034</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>22.05842113</v>
+      </c>
+      <c r="E14" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>6492400775.188599</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>35.72800996</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0.95298552</v>
+      </c>
+      <c r="E16" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0.1994048</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6492400775.188599</v>
+        <v>6712287732.076562</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>35.72800996</v>
+        <v>36.59487862</v>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4008398749.148034</v>
+        <v>3971580238.866385</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.05842113</v>
+        <v>21.65275128</v>
       </c>
       <c r="E3" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2424619185.940132</v>
+        <v>2402493014.951586</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.34280206</v>
+        <v>13.09820791</v>
       </c>
       <c r="E4" t="n">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2158273413.781404</v>
+        <v>2171291587.879643</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>11.8770878</v>
+        <v>11.83771544</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1992324194.81826</v>
+        <v>1993638069.686081</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.96386085</v>
+        <v>10.86916206</v>
       </c>
       <c r="E6" t="n">
         <v>137</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>886313475.1740601</v>
+        <v>879311188.2211212</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.8774279</v>
+        <v>4.79393725</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>173174043.2128489</v>
+        <v>175313403.5272729</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.95298552</v>
+        <v>0.95579525</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.1994048</v>
+        <v>0.19755219</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>18171739156.51621</v>
+        <v>18342150554.46152</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1049,6 +1049,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>2171291587.879643</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>11.83771544</v>
+      </c>
+      <c r="E18" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>2402493014.951586</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>13.09820791</v>
+      </c>
+      <c r="E19" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>879311188.2211212</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>4.79393725</v>
+      </c>
+      <c r="E20" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1993638069.686081</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>10.86916206</v>
+      </c>
+      <c r="E21" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>3971580238.866385</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>21.65275128</v>
+      </c>
+      <c r="E22" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>6712287732.076562</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>36.59487862</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>175313403.5272729</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.95579525</v>
+      </c>
+      <c r="E24" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0.19755219</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6712287732.076562</v>
+        <v>6461317399.805664</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>36.59487862</v>
+        <v>35.60398826</v>
       </c>
       <c r="E2" t="n">
-        <v>1216</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3971580238.866385</v>
+        <v>3981790674.579305</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.65275128</v>
+        <v>21.94097886</v>
       </c>
       <c r="E3" t="n">
         <v>229</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2402493014.951586</v>
+        <v>2398495623.05719</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.09820791</v>
+        <v>13.21650133</v>
       </c>
       <c r="E4" t="n">
         <v>298</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2171291587.879643</v>
+        <v>2174731593.649778</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>11.83771544</v>
+        <v>11.98348779</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1993638069.686081</v>
+        <v>2021737430.081003</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.86916206</v>
+        <v>11.14043952</v>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>879311188.2211212</v>
+        <v>891495233.9156833</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.79393725</v>
+        <v>4.91243254</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175313403.5272729</v>
+        <v>181931613.7154169</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.95579525</v>
+        <v>1.00250315</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.19755219</v>
+        <v>0.19966855</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>18342150554.46152</v>
+        <v>18147734888.05692</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1217,6 +1217,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>2174731593.649778</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>11.98348779</v>
+      </c>
+      <c r="E26" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>2398495623.05719</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>13.21650133</v>
+      </c>
+      <c r="E27" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>891495233.9156833</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>4.91243254</v>
+      </c>
+      <c r="E28" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>2021737430.081003</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>11.14043952</v>
+      </c>
+      <c r="E29" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>3981790674.579305</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>21.94097886</v>
+      </c>
+      <c r="E30" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>6461317399.805664</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>35.60398826</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>181931613.7154169</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1.00250315</v>
+      </c>
+      <c r="E32" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0.19966855</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6461317399.805664</v>
+        <v>6529771242.979856</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>35.60398826</v>
+        <v>35.86793827</v>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3981790674.579305</v>
+        <v>4025918791.820355</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.94097886</v>
+        <v>22.11431325</v>
       </c>
       <c r="E3" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2398495623.05719</v>
+        <v>2390384111.083554</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.21650133</v>
+        <v>13.13034508</v>
       </c>
       <c r="E4" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2174731593.649778</v>
+        <v>2172369069.119945</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>11.98348779</v>
+        <v>11.93279164</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2021737430.081003</v>
+        <v>1985690652.323662</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.14043952</v>
+        <v>10.90736981</v>
       </c>
       <c r="E6" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>891495233.9156833</v>
+        <v>886068419.1238271</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.91243254</v>
+        <v>4.86716091</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>181931613.7154169</v>
+        <v>178598863.8421169</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00250315</v>
+        <v>0.98104096</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.19966855</v>
+        <v>0.19904008</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>18147734888.05692</v>
+        <v>18205036469.54619</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1385,6 +1385,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>2172369069.119945</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>11.93279164</v>
+      </c>
+      <c r="E34" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>2390384111.083554</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>13.13034508</v>
+      </c>
+      <c r="E35" t="n">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>886068419.1238271</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>4.86716091</v>
+      </c>
+      <c r="E36" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1985690652.323662</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>10.90736981</v>
+      </c>
+      <c r="E37" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>4025918791.820355</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>22.11431325</v>
+      </c>
+      <c r="E38" t="n">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>6529771242.979856</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>35.86793827</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>178598863.8421169</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0.98104096</v>
+      </c>
+      <c r="E40" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0.19904008</v>
+      </c>
+      <c r="E41" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6529771242.979856</v>
+        <v>6306060709.43778</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>35.86793827</v>
+        <v>35.33719171</v>
       </c>
       <c r="E2" t="n">
-        <v>1214</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4025918791.820355</v>
+        <v>3928627851.6525</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.11431325</v>
+        <v>22.01480163</v>
       </c>
       <c r="E3" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2390384111.083554</v>
+        <v>2419929182.376888</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.13034508</v>
+        <v>13.5605262</v>
       </c>
       <c r="E4" t="n">
-        <v>297</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2172369069.119945</v>
+        <v>2160419676.096912</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>11.93279164</v>
+        <v>12.1063161</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1985690652.323662</v>
+        <v>1939048650.340436</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.90736981</v>
+        <v>10.86582211</v>
       </c>
       <c r="E6" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>886068419.1238271</v>
+        <v>879813706.291942</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.86716091</v>
+        <v>4.93020081</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>178598863.8421169</v>
+        <v>177960723.4363399</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.98104096</v>
+        <v>0.9972362299999999</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>36235319.252875</v>
+        <v>33532423.89534</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.19904008</v>
+        <v>0.18790521</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>18205036469.54619</v>
+        <v>17845392923.52814</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1553,6 +1553,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>2160419676.096912</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>12.1063161</v>
+      </c>
+      <c r="E42" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>2419929182.376888</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>13.5605262</v>
+      </c>
+      <c r="E43" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>879813706.291942</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>4.93020081</v>
+      </c>
+      <c r="E44" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>1939048650.340436</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>10.86582211</v>
+      </c>
+      <c r="E45" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>3928627851.6525</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>22.01480163</v>
+      </c>
+      <c r="E46" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>6306060709.43778</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>35.33719171</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>177960723.4363399</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.9972362299999999</v>
+      </c>
+      <c r="E48" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>33532423.89534</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0.18790521</v>
+      </c>
+      <c r="E49" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6306060709.43778</v>
+        <v>6175564873.380866</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>35.33719171</v>
+        <v>34.87625451</v>
       </c>
       <c r="E2" t="n">
-        <v>1216</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3928627851.6525</v>
+        <v>3856706828.191245</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.01480163</v>
+        <v>21.78059686</v>
       </c>
       <c r="E3" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2419929182.376888</v>
+        <v>2410328442.222064</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.5605262</v>
+        <v>13.61223304</v>
       </c>
       <c r="E4" t="n">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2160419676.096912</v>
+        <v>2173967215.69673</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.1063161</v>
+        <v>12.27739251</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1939048650.340436</v>
+        <v>1989039262.080312</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.86582211</v>
+        <v>11.23301932</v>
       </c>
       <c r="E6" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>879813706.291942</v>
+        <v>885937739.9604901</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.93020081</v>
+        <v>5.00329779</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>177960723.4363399</v>
+        <v>179296265.0160269</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.9972362299999999</v>
+        <v>1.01256845</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>33532423.89534</v>
+        <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.18790521</v>
+        <v>0.20463751</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17845392923.52814</v>
+        <v>17707075945.80061</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1721,6 +1721,174 @@
         <v>6</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>2173967215.69673</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>12.27739251</v>
+      </c>
+      <c r="E50" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>2410328442.222064</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>13.61223304</v>
+      </c>
+      <c r="E51" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>885937739.9604901</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>5.00329779</v>
+      </c>
+      <c r="E52" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>1989039262.080312</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>11.23301932</v>
+      </c>
+      <c r="E53" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>3856706828.191245</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>21.78059686</v>
+      </c>
+      <c r="E54" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>6175564873.380866</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>34.87625451</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>179296265.0160269</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>1.01256845</v>
+      </c>
+      <c r="E56" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0.20463751</v>
+      </c>
+      <c r="E57" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6175564873.380866</v>
+        <v>6331071541.883705</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.87625451</v>
+        <v>35.45847297</v>
       </c>
       <c r="E2" t="n">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3856706828.191245</v>
+        <v>3836540883.141033</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.78059686</v>
+        <v>21.48733912</v>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2410328442.222064</v>
+        <v>2408725300.718084</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.61223304</v>
+        <v>13.49056323</v>
       </c>
       <c r="E4" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2173967215.69673</v>
+        <v>2179040169.069197</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.27739251</v>
+        <v>12.20416424</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1989039262.080312</v>
+        <v>1995446232.59531</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.23301932</v>
+        <v>11.17590851</v>
       </c>
       <c r="E6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>885937739.9604901</v>
+        <v>889165108.8002241</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.00329779</v>
+        <v>4.97995272</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>179296265.0160269</v>
+        <v>178666001.6927119</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01256845</v>
+        <v>1.00065582</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20463751</v>
+        <v>0.20294338</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17707075945.80061</v>
+        <v>17854890557.15314</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1889,6 +1889,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>2179040169.069197</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>12.20416424</v>
+      </c>
+      <c r="E58" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>2408725300.718084</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>13.49056323</v>
+      </c>
+      <c r="E59" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>889165108.8002241</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>4.97995272</v>
+      </c>
+      <c r="E60" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1995446232.59531</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>11.17590851</v>
+      </c>
+      <c r="E61" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>3836540883.141033</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>21.48733912</v>
+      </c>
+      <c r="E62" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>6331071541.883705</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>35.45847297</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>178666001.6927119</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>1.00065582</v>
+      </c>
+      <c r="E64" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0.20294338</v>
+      </c>
+      <c r="E65" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -488,13 +488,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6331071541.883705</v>
+        <v>6338905785.293786</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>35.45847297</v>
+        <v>35.49930683</v>
       </c>
       <c r="E2" t="n">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="3">
@@ -509,13 +509,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3836540883.141033</v>
+        <v>3842313361.744844</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.48733912</v>
+        <v>21.51782431</v>
       </c>
       <c r="E3" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4">
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2408725300.718084</v>
+        <v>2401797950.186281</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.49056323</v>
+        <v>13.45061203</v>
       </c>
       <c r="E4" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5">
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2179040169.069197</v>
+        <v>2177653562.870558</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.20416424</v>
+        <v>12.19535273</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1995446232.59531</v>
+        <v>1995621913.653009</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.17590851</v>
+        <v>11.17593431</v>
       </c>
       <c r="E6" t="n">
         <v>136</v>
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>889165108.8002241</v>
+        <v>885845494.8726742</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.97995272</v>
+        <v>4.96093523</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>178666001.6927119</v>
+        <v>178047908.5790689</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00065582</v>
+        <v>0.99710858</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20294338</v>
+        <v>0.20292599</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17854890557.15314</v>
+        <v>17856421296.4531</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>2179040169.069197</v>
+        <v>2177653562.870558</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>12.20416424</v>
+        <v>12.19535273</v>
       </c>
       <c r="E58" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59">
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>2408725300.718084</v>
+        <v>2401797950.186281</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>13.49056323</v>
+        <v>13.45061203</v>
       </c>
       <c r="E59" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="60">
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>889165108.8002241</v>
+        <v>885845494.8726742</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>4.97995272</v>
+        <v>4.96093523</v>
       </c>
       <c r="E60" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>1995446232.59531</v>
+        <v>1995621913.653009</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>11.17590851</v>
+        <v>11.17593431</v>
       </c>
       <c r="E61" t="n">
         <v>136</v>
@@ -1985,13 +1985,13 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>3836540883.141033</v>
+        <v>3842313361.744844</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>21.48733912</v>
+        <v>21.51782431</v>
       </c>
       <c r="E62" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="63">
@@ -2006,13 +2006,13 @@
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>6331071541.883705</v>
+        <v>6338905785.293786</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>35.45847297</v>
+        <v>35.49930683</v>
       </c>
       <c r="E63" t="n">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="64">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>178666001.6927119</v>
+        <v>178047908.5790689</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>1.00065582</v>
+        <v>0.99710858</v>
       </c>
       <c r="E64" t="n">
         <v>22</v>
@@ -2051,7 +2051,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0.20294338</v>
+        <v>0.20292599</v>
       </c>
       <c r="E65" t="n">
         <v>7</v>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6338905785.293786</v>
+        <v>6241080915.499789</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>35.49930683</v>
+        <v>34.84007267</v>
       </c>
       <c r="E2" t="n">
         <v>1214</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3842313361.744844</v>
+        <v>3968265208.78482</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.51782431</v>
+        <v>22.15235632</v>
       </c>
       <c r="E3" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2401797950.186281</v>
+        <v>2405639728.555096</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.45061203</v>
+        <v>13.42919025</v>
       </c>
       <c r="E4" t="n">
         <v>298</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2177653562.870558</v>
+        <v>2193190127.284426</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.19535273</v>
+        <v>12.24321627</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1995621913.653009</v>
+        <v>2003940652.906156</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.17593431</v>
+        <v>11.18675417</v>
       </c>
       <c r="E6" t="n">
         <v>136</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>885845494.8726742</v>
+        <v>885830083.7133422</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.96093523</v>
+        <v>4.94503835</v>
       </c>
       <c r="E7" t="n">
         <v>45</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>178047908.5790689</v>
+        <v>179330872.6465179</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.99710858</v>
+        <v>1.00109271</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20292599</v>
+        <v>0.20227925</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17856421296.4531</v>
+        <v>17913512908.64302</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2057,6 +2057,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>2193190127.284426</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>12.24321627</v>
+      </c>
+      <c r="E66" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>2405639728.555096</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>13.42919025</v>
+      </c>
+      <c r="E67" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>885830083.7133422</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>4.94503835</v>
+      </c>
+      <c r="E68" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>2003940652.906156</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>11.18675417</v>
+      </c>
+      <c r="E69" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>3968265208.78482</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>22.15235632</v>
+      </c>
+      <c r="E70" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>6241080915.499789</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>34.84007267</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>179330872.6465179</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>1.00109271</v>
+      </c>
+      <c r="E72" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0.20227925</v>
+      </c>
+      <c r="E73" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6241080915.499789</v>
+        <v>6032678732.608068</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.84007267</v>
+        <v>34.04941717</v>
       </c>
       <c r="E2" t="n">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3968265208.78482</v>
+        <v>3989517201.795234</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.15235632</v>
+        <v>22.51748212</v>
       </c>
       <c r="E3" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2405639728.555096</v>
+        <v>2401370555.98562</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.42919025</v>
+        <v>13.55372488</v>
       </c>
       <c r="E4" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2193190127.284426</v>
+        <v>2196085245.875914</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.24321627</v>
+        <v>12.3950613</v>
       </c>
       <c r="E5" t="n">
         <v>50</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2003940652.906156</v>
+        <v>1996241115.274479</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.18675417</v>
+        <v>11.26710861</v>
       </c>
       <c r="E6" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>885830083.7133422</v>
+        <v>885821621.8383652</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.94503835</v>
+        <v>4.9997209</v>
       </c>
       <c r="E7" t="n">
         <v>45</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>179330872.6465179</v>
+        <v>179471631.3922109</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00109271</v>
+        <v>1.012967</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20227925</v>
+        <v>0.20451802</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17913512908.64302</v>
+        <v>17717421424.02277</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2225,6 +2225,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>2196085245.875914</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>12.3950613</v>
+      </c>
+      <c r="E74" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>2401370555.98562</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>13.55372488</v>
+      </c>
+      <c r="E75" t="n">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>885821621.8383652</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>4.9997209</v>
+      </c>
+      <c r="E76" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>1996241115.274479</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>11.26710861</v>
+      </c>
+      <c r="E77" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>3989517201.795234</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>22.51748212</v>
+      </c>
+      <c r="E78" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>6032678732.608068</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>34.04941717</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>179471631.3922109</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>1.012967</v>
+      </c>
+      <c r="E80" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0.20451802</v>
+      </c>
+      <c r="E81" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6032678732.608068</v>
+        <v>6046754142.555535</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.04941717</v>
+        <v>34.1341793</v>
       </c>
       <c r="E2" t="n">
-        <v>1215</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3989517201.795234</v>
+        <v>3978158179.056409</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.51748212</v>
+        <v>22.45686882</v>
       </c>
       <c r="E3" t="n">
         <v>231</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2401370555.98562</v>
+        <v>2404799376.832213</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.55372488</v>
+        <v>13.57519277</v>
       </c>
       <c r="E4" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2196085245.875914</v>
+        <v>2196164154.404851</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.3950613</v>
+        <v>12.39743824</v>
       </c>
       <c r="E5" t="n">
         <v>50</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1996241115.274479</v>
+        <v>1993750432.400999</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.26710861</v>
+        <v>11.25480434</v>
       </c>
       <c r="E6" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>885821621.8383652</v>
+        <v>885625333.5433872</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.9997209</v>
+        <v>4.99939194</v>
       </c>
       <c r="E7" t="n">
         <v>45</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>179471631.3922109</v>
+        <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.012967</v>
+        <v>0.9775747</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20451802</v>
+        <v>0.20454989</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17717421424.02277</v>
+        <v>17714660981.25912</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2393,6 +2393,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>2196164154.404851</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>12.39743824</v>
+      </c>
+      <c r="E82" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>2404799376.832213</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>13.57519277</v>
+      </c>
+      <c r="E83" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>885625333.5433872</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>4.99939194</v>
+      </c>
+      <c r="E84" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>1993750432.400999</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>11.25480434</v>
+      </c>
+      <c r="E85" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>3978158179.056409</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>22.45686882</v>
+      </c>
+      <c r="E86" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>6046754142.555535</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>34.1341793</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0.9775747</v>
+      </c>
+      <c r="E88" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0.20454989</v>
+      </c>
+      <c r="E89" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6046754142.555535</v>
+        <v>6201136236.518588</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.1341793</v>
+        <v>34.72586391</v>
       </c>
       <c r="E2" t="n">
-        <v>1213</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3978158179.056409</v>
+        <v>3987645691.098222</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.45686882</v>
+        <v>22.33049498</v>
       </c>
       <c r="E3" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2404799376.832213</v>
+        <v>2372453690.058927</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.57519277</v>
+        <v>13.28554975</v>
       </c>
       <c r="E4" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2196164154.404851</v>
+        <v>2198031511.496174</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.39743824</v>
+        <v>12.30879959</v>
       </c>
       <c r="E5" t="n">
         <v>50</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1993750432.400999</v>
+        <v>2000458929.597376</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.25480434</v>
+        <v>11.20240903</v>
       </c>
       <c r="E6" t="n">
         <v>135</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>885625333.5433872</v>
+        <v>885129253.9612691</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.99939194</v>
+        <v>4.95665259</v>
       </c>
       <c r="E7" t="n">
         <v>45</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>173174043.2128489</v>
+        <v>176308834.0065689</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.9775747</v>
+        <v>0.98731528</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20454989</v>
+        <v>0.20291487</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17714660981.25912</v>
+        <v>17857399465.99</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2561,6 +2561,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>2198031511.496174</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>12.30879959</v>
+      </c>
+      <c r="E90" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>2372453690.058927</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>13.28554975</v>
+      </c>
+      <c r="E91" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>885129253.9612691</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>4.95665259</v>
+      </c>
+      <c r="E92" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>2000458929.597376</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>11.20240903</v>
+      </c>
+      <c r="E93" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>3987645691.098222</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>22.33049498</v>
+      </c>
+      <c r="E94" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>6201136236.518588</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>34.72586391</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>176308834.0065689</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.98731528</v>
+      </c>
+      <c r="E96" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.20291487</v>
+      </c>
+      <c r="E97" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6201136236.518588</v>
+        <v>6267320340.965001</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.72586391</v>
+        <v>35.00419805</v>
       </c>
       <c r="E2" t="n">
-        <v>1219</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3987645691.098222</v>
+        <v>3924919261.445942</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.33049498</v>
+        <v>21.92143431</v>
       </c>
       <c r="E3" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2372453690.058927</v>
+        <v>2414489248.317061</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.28554975</v>
+        <v>13.48539013</v>
       </c>
       <c r="E4" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2198031511.496174</v>
+        <v>2197195797.348855</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.30879959</v>
+        <v>12.27176411</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2000458929.597376</v>
+        <v>1996803060.224689</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.20240903</v>
+        <v>11.15253186</v>
       </c>
       <c r="E6" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>885129253.9612691</v>
+        <v>887995674.3633192</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.95665259</v>
+        <v>4.95962784</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>176308834.0065689</v>
+        <v>179523301.2976289</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.98731528</v>
+        <v>1.00267241</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20291487</v>
+        <v>0.20238128</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17857399465.99</v>
+        <v>17904482003.21537</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2729,6 +2729,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>2197195797.348855</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>12.27176411</v>
+      </c>
+      <c r="E98" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>2414489248.317061</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>13.48539013</v>
+      </c>
+      <c r="E99" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>887995674.3633192</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>4.95962784</v>
+      </c>
+      <c r="E100" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>1996803060.224689</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>11.15253186</v>
+      </c>
+      <c r="E101" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>3924919261.445942</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>21.92143431</v>
+      </c>
+      <c r="E102" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>6267320340.965001</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>35.00419805</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>179523301.2976289</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>1.00267241</v>
+      </c>
+      <c r="E104" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0.20238128</v>
+      </c>
+      <c r="E105" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6267320340.965001</v>
+        <v>5807423381.380778</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>35.00419805</v>
+        <v>33.06990522</v>
       </c>
       <c r="E2" t="n">
-        <v>1215</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3924919261.445942</v>
+        <v>4084885597.624835</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.92143431</v>
+        <v>23.26105239</v>
       </c>
       <c r="E3" t="n">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2414489248.317061</v>
+        <v>2440141257.516134</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.48539013</v>
+        <v>13.89518807</v>
       </c>
       <c r="E4" t="n">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2197195797.348855</v>
+        <v>2208061115.318271</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.27176411</v>
+        <v>12.57362637</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1996803060.224689</v>
+        <v>1953418398.125191</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.15253186</v>
+        <v>11.12358391</v>
       </c>
       <c r="E6" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>887995674.3633192</v>
+        <v>861780457.2880982</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.95962784</v>
+        <v>4.90733948</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>179523301.2976289</v>
+        <v>165313300.3850649</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00267241</v>
+        <v>0.94136329</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>36235319.252875</v>
+        <v>40028885.516623</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20238128</v>
+        <v>0.22794127</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17904482003.21537</v>
+        <v>17561052393.15499</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2897,6 +2897,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>2208061115.318271</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>12.57362637</v>
+      </c>
+      <c r="E106" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>2440141257.516134</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>13.89518807</v>
+      </c>
+      <c r="E107" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>861780457.2880982</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>4.90733948</v>
+      </c>
+      <c r="E108" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>1953418398.125191</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>11.12358391</v>
+      </c>
+      <c r="E109" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>4084885597.624835</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>23.26105239</v>
+      </c>
+      <c r="E110" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>5807423381.380778</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>33.06990522</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>165313300.3850649</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0.94136329</v>
+      </c>
+      <c r="E112" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>40028885.516623</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0.22794127</v>
+      </c>
+      <c r="E113" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5807423381.380778</v>
+        <v>5857511467.437473</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.06990522</v>
+        <v>33.45865007</v>
       </c>
       <c r="E2" t="n">
-        <v>1212</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4084885597.624835</v>
+        <v>3966669530.923533</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>23.26105239</v>
+        <v>22.65798514</v>
       </c>
       <c r="E3" t="n">
-        <v>238</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2440141257.516134</v>
+        <v>2416074306.548095</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.89518807</v>
+        <v>13.80084106</v>
       </c>
       <c r="E4" t="n">
-        <v>305</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2208061115.318271</v>
+        <v>2218695640.668798</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.57362637</v>
+        <v>12.67339577</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1953418398.125191</v>
+        <v>1958825149.609352</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.12358391</v>
+        <v>11.18899137</v>
       </c>
       <c r="E6" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>861780457.2880982</v>
+        <v>873473297.2603872</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.90733948</v>
+        <v>4.98936068</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>165313300.3850649</v>
+        <v>179233147.3493089</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.94136329</v>
+        <v>1.0237964</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>40028885.516623</v>
+        <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.22794127</v>
+        <v>0.20697951</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17561052393.15499</v>
+        <v>17506717859.04982</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3065,6 +3065,174 @@
         <v>8</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>2218695640.668798</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>12.67339577</v>
+      </c>
+      <c r="E114" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>2416074306.548095</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>13.80084106</v>
+      </c>
+      <c r="E115" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>873473297.2603872</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>4.98936068</v>
+      </c>
+      <c r="E116" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>1958825149.609352</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>11.18899137</v>
+      </c>
+      <c r="E117" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>3966669530.923533</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>22.65798514</v>
+      </c>
+      <c r="E118" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>5857511467.437473</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>33.45865007</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>179233147.3493089</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>1.0237964</v>
+      </c>
+      <c r="E120" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0.20697951</v>
+      </c>
+      <c r="E121" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5857511467.437473</v>
+        <v>5872940619.430573</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.45865007</v>
+        <v>33.55663783</v>
       </c>
       <c r="E2" t="n">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3966669530.923533</v>
+        <v>3972227570.72269</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.65798514</v>
+        <v>22.69639872</v>
       </c>
       <c r="E3" t="n">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2416074306.548095</v>
+        <v>2429887170.147285</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.80084106</v>
+        <v>13.88381886</v>
       </c>
       <c r="E4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2218695640.668798</v>
+        <v>2211534509.408753</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.67339577</v>
+        <v>12.63620176</v>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1958825149.609352</v>
+        <v>1914582654.44224</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.18899137</v>
+        <v>10.93948686</v>
       </c>
       <c r="E6" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>873473297.2603872</v>
+        <v>885304391.7302842</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.98936068</v>
+        <v>5.05842657</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>179233147.3493089</v>
+        <v>178864199.5622369</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.0237964</v>
+        <v>1.02198908</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20697951</v>
+        <v>0.20704032</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17506717859.04982</v>
+        <v>17501576434.69694</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3233,6 +3233,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v>2211534509.408753</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>12.63620176</v>
+      </c>
+      <c r="E122" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>2429887170.147285</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>13.88381886</v>
+      </c>
+      <c r="E123" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>885304391.7302842</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>5.05842657</v>
+      </c>
+      <c r="E124" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>1914582654.44224</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>10.93948686</v>
+      </c>
+      <c r="E125" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v>3972227570.72269</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>22.69639872</v>
+      </c>
+      <c r="E126" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>5872940619.430573</v>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>33.55663783</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>178864199.5622369</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>1.02198908</v>
+      </c>
+      <c r="E128" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>0.20704032</v>
+      </c>
+      <c r="E129" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5872940619.430573</v>
+        <v>5875658324.088663</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.55663783</v>
+        <v>33.5560142</v>
       </c>
       <c r="E2" t="n">
         <v>1214</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3972227570.72269</v>
+        <v>3963283922.433371</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.69639872</v>
+        <v>22.63440184</v>
       </c>
       <c r="E3" t="n">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2429887170.147285</v>
+        <v>2428310730.597656</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.88381886</v>
+        <v>13.86813611</v>
       </c>
       <c r="E4" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2211534509.408753</v>
+        <v>2207293239.97974</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.63620176</v>
+        <v>12.60590035</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1914582654.44224</v>
+        <v>1935257411.269078</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.93948686</v>
+        <v>11.05229773</v>
       </c>
       <c r="E6" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>885304391.7302842</v>
+        <v>885196358.1447681</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.05842657</v>
+        <v>5.05537591</v>
       </c>
       <c r="E7" t="n">
         <v>45</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>178864199.5622369</v>
+        <v>178765401.6775069</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02198908</v>
+        <v>1.02093315</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20704032</v>
+        <v>0.20694071</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17501576434.69694</v>
+        <v>17510000707.44366</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:E137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3401,6 +3401,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>2207293239.97974</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>12.60590035</v>
+      </c>
+      <c r="E130" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>2428310730.597656</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>13.86813611</v>
+      </c>
+      <c r="E131" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v>885196358.1447681</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>5.05537591</v>
+      </c>
+      <c r="E132" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v>1935257411.269078</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>11.05229773</v>
+      </c>
+      <c r="E133" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>3963283922.433371</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>22.63440184</v>
+      </c>
+      <c r="E134" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>5875658324.088663</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>33.5560142</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>178765401.6775069</v>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>1.02093315</v>
+      </c>
+      <c r="E136" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>0.20694071</v>
+      </c>
+      <c r="E137" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5875658324.088663</v>
+        <v>5817956787.880551</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.5560142</v>
+        <v>33.26680493</v>
       </c>
       <c r="E2" t="n">
-        <v>1214</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3963283922.433371</v>
+        <v>3960811961.270478</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.63440184</v>
+        <v>22.64773763</v>
       </c>
       <c r="E3" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2428310730.597656</v>
+        <v>2409186137.210111</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.86813611</v>
+        <v>13.7756137</v>
       </c>
       <c r="E4" t="n">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2207293239.97974</v>
+        <v>2219828111.51674</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.60590035</v>
+        <v>12.69287337</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1935257411.269078</v>
+        <v>1936203874.671554</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.05229773</v>
+        <v>11.07112324</v>
       </c>
       <c r="E6" t="n">
         <v>134</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>885196358.1447681</v>
+        <v>924509034.6484132</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.05537591</v>
+        <v>5.28629944</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>178765401.6775069</v>
+        <v>184044148.0925579</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02093315</v>
+        <v>1.05235583</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20694071</v>
+        <v>0.20719186</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17510000707.44366</v>
+        <v>17488775374.54328</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3569,6 +3569,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>2219828111.51674</v>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>12.69287337</v>
+      </c>
+      <c r="E138" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>2409186137.210111</v>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>13.7756137</v>
+      </c>
+      <c r="E139" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>924509034.6484132</v>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>5.28629944</v>
+      </c>
+      <c r="E140" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>1936203874.671554</v>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>11.07112324</v>
+      </c>
+      <c r="E141" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>3960811961.270478</v>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>22.64773763</v>
+      </c>
+      <c r="E142" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>5817956787.880551</v>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>33.26680493</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>184044148.0925579</v>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>1.05235583</v>
+      </c>
+      <c r="E144" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>0.20719186</v>
+      </c>
+      <c r="E145" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5817956787.880551</v>
+        <v>5851777126.915024</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.26680493</v>
+        <v>33.49811979</v>
       </c>
       <c r="E2" t="n">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3960811961.270478</v>
+        <v>3938798665.106073</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.64773763</v>
+        <v>22.54739828</v>
       </c>
       <c r="E3" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2409186137.210111</v>
+        <v>2413315734.951137</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.7756137</v>
+        <v>13.81486988</v>
       </c>
       <c r="E4" t="n">
         <v>298</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2219828111.51674</v>
+        <v>2216035920.410485</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.69287337</v>
+        <v>12.68555434</v>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1936203874.671554</v>
+        <v>1948903910.829417</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.07112324</v>
+        <v>11.15637442</v>
       </c>
       <c r="E6" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>924509034.6484132</v>
+        <v>885118434.0287251</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.28629944</v>
+        <v>5.06680324</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>184044148.0925579</v>
+        <v>178786770.4150799</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.05235583</v>
+        <v>1.02345331</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20719186</v>
+        <v>0.20742674</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17488775374.54328</v>
+        <v>17468971881.90882</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E145"/>
+  <dimension ref="A1:E153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3737,6 +3737,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>2216035920.410485</v>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>12.68555434</v>
+      </c>
+      <c r="E146" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>2413315734.951137</v>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>13.81486988</v>
+      </c>
+      <c r="E147" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>885118434.0287251</v>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>5.06680324</v>
+      </c>
+      <c r="E148" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v>1948903910.829417</v>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>11.15637442</v>
+      </c>
+      <c r="E149" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>3938798665.106073</v>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>22.54739828</v>
+      </c>
+      <c r="E150" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>5851777126.915024</v>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>33.49811979</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>178786770.4150799</v>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>1.02345331</v>
+      </c>
+      <c r="E152" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>0.20742674</v>
+      </c>
+      <c r="E153" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5851777126.915024</v>
+        <v>5900007081.891464</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.49811979</v>
+        <v>33.71918153</v>
       </c>
       <c r="E2" t="n">
         <v>1212</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3938798665.106073</v>
+        <v>3950155242.113533</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.54739828</v>
+        <v>22.57556641</v>
       </c>
       <c r="E3" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2413315734.951137</v>
+        <v>2420444952.901846</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.81486988</v>
+        <v>13.8331059</v>
       </c>
       <c r="E4" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2216035920.410485</v>
+        <v>2218120620.655385</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.68555434</v>
+        <v>12.67680035</v>
       </c>
       <c r="E5" t="n">
         <v>50</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1948903910.829417</v>
+        <v>1948324427.014131</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.15637442</v>
+        <v>11.13488579</v>
       </c>
       <c r="E6" t="n">
         <v>137</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>885118434.0287251</v>
+        <v>845842504.6601372</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.06680324</v>
+        <v>4.83408182</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>178786770.4150799</v>
+        <v>178349961.8887709</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02345331</v>
+        <v>1.01928941</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20742674</v>
+        <v>0.20708879</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17468971881.90882</v>
+        <v>17497480110.37814</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E153"/>
+  <dimension ref="A1:E161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3905,6 +3905,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v>2218120620.655385</v>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>12.67680035</v>
+      </c>
+      <c r="E154" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>2420444952.901846</v>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>13.8331059</v>
+      </c>
+      <c r="E155" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>845842504.6601372</v>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>4.83408182</v>
+      </c>
+      <c r="E156" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>1948324427.014131</v>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>11.13488579</v>
+      </c>
+      <c r="E157" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>3950155242.113533</v>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>22.57556641</v>
+      </c>
+      <c r="E158" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>5900007081.891464</v>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>33.71918153</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>178349961.8887709</v>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>1.01928941</v>
+      </c>
+      <c r="E160" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>0.20708879</v>
+      </c>
+      <c r="E161" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5900007081.891464</v>
+        <v>5811186118.928448</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.71918153</v>
+        <v>33.28505611</v>
       </c>
       <c r="E2" t="n">
         <v>1212</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3950155242.113533</v>
+        <v>3945792519.014203</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.57556641</v>
+        <v>22.60053674</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2420444952.901846</v>
+        <v>2419190790.192969</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.8331059</v>
+        <v>13.85653454</v>
       </c>
       <c r="E4" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2218120620.655385</v>
+        <v>2228845260.190838</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.67680035</v>
+        <v>12.76628179</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1948324427.014131</v>
+        <v>1955974867.050313</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.13488579</v>
+        <v>11.20334676</v>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>845842504.6601372</v>
+        <v>881734941.4962542</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4.83408182</v>
+        <v>5.05036259</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>178349961.8887709</v>
+        <v>179884478.0837109</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01928941</v>
+        <v>1.0303344</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20708879</v>
+        <v>0.20754707</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17497480110.37814</v>
+        <v>17458844294.20961</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E161"/>
+  <dimension ref="A1:E169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4073,6 +4073,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>2228845260.190838</v>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>12.76628179</v>
+      </c>
+      <c r="E162" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>2419190790.192969</v>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>13.85653454</v>
+      </c>
+      <c r="E163" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>881734941.4962542</v>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>5.05036259</v>
+      </c>
+      <c r="E164" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>1955974867.050313</v>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>11.20334676</v>
+      </c>
+      <c r="E165" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>3945792519.014203</v>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>22.60053674</v>
+      </c>
+      <c r="E166" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>5811186118.928448</v>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>33.28505611</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>179884478.0837109</v>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>1.0303344</v>
+      </c>
+      <c r="E168" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>0.20754707</v>
+      </c>
+      <c r="E169" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5811186118.928448</v>
+        <v>5813016226.554807</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.28505611</v>
+        <v>33.38698375</v>
       </c>
       <c r="E2" t="n">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3945792519.014203</v>
+        <v>3883151865.086282</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.60053674</v>
+        <v>22.30283267</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2419190790.192969</v>
+        <v>2428352160.366689</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.85653454</v>
+        <v>13.94720932</v>
       </c>
       <c r="E4" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2228845260.190838</v>
+        <v>2236149036.177119</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.76628179</v>
+        <v>12.84329316</v>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1955974867.050313</v>
+        <v>1957500055.570525</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.20334676</v>
+        <v>11.24287633</v>
       </c>
       <c r="E6" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>881734941.4962542</v>
+        <v>879461938.8970662</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.05036259</v>
+        <v>5.05117831</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>179884478.0837109</v>
+        <v>177158816.9800219</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.0303344</v>
+        <v>1.01750938</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20754707</v>
+        <v>0.20811709</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17458844294.20961</v>
+        <v>17411025418.88538</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:E177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4241,6 +4241,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>2236149036.177119</v>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>12.84329316</v>
+      </c>
+      <c r="E170" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>2428352160.366689</v>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>13.94720932</v>
+      </c>
+      <c r="E171" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n">
+        <v>879461938.8970662</v>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>5.05117831</v>
+      </c>
+      <c r="E172" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n">
+        <v>1957500055.570525</v>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>11.24287633</v>
+      </c>
+      <c r="E173" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v>3883151865.086282</v>
+      </c>
+      <c r="D174" s="3" t="n">
+        <v>22.30283267</v>
+      </c>
+      <c r="E174" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n">
+        <v>5813016226.554807</v>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>33.38698375</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v>177158816.9800219</v>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>1.01750938</v>
+      </c>
+      <c r="E176" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>0.20811709</v>
+      </c>
+      <c r="E177" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5813016226.554807</v>
+        <v>5916935933.616653</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.38698375</v>
+        <v>33.90731615</v>
       </c>
       <c r="E2" t="n">
-        <v>1211</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3883151865.086282</v>
+        <v>3895923808.758009</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.30283267</v>
+        <v>22.32579865</v>
       </c>
       <c r="E3" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2428352160.366689</v>
+        <v>2439137848.61445</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.94720932</v>
+        <v>13.97760921</v>
       </c>
       <c r="E4" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2236149036.177119</v>
+        <v>2150714229.62248</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.84329316</v>
+        <v>12.32478231</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1957500055.570525</v>
+        <v>1955703569.021117</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.24287633</v>
+        <v>11.20726335</v>
       </c>
       <c r="E6" t="n">
         <v>139</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>879461938.8970662</v>
+        <v>878688702.7877141</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.05117831</v>
+        <v>5.03537236</v>
       </c>
       <c r="E7" t="n">
         <v>43</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>177158816.9800219</v>
+        <v>176982833.7347319</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01750938</v>
+        <v>1.01420954</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20811709</v>
+        <v>0.20764842</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17411025418.88538</v>
+        <v>17450322245.40804</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E177"/>
+  <dimension ref="A1:E185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4409,6 +4409,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>2150714229.62248</v>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>12.32478231</v>
+      </c>
+      <c r="E178" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="n">
+        <v>2439137848.61445</v>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>13.97760921</v>
+      </c>
+      <c r="E179" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="n">
+        <v>878688702.7877141</v>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>5.03537236</v>
+      </c>
+      <c r="E180" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="n">
+        <v>1955703569.021117</v>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>11.20726335</v>
+      </c>
+      <c r="E181" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="n">
+        <v>3895923808.758009</v>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>22.32579865</v>
+      </c>
+      <c r="E182" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="n">
+        <v>5916935933.616653</v>
+      </c>
+      <c r="D183" s="3" t="n">
+        <v>33.90731615</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="n">
+        <v>176982833.7347319</v>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>1.01420954</v>
+      </c>
+      <c r="E184" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D185" s="3" t="n">
+        <v>0.20764842</v>
+      </c>
+      <c r="E185" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5916935933.616653</v>
+        <v>5816299104.73747</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.90731615</v>
+        <v>33.41764815</v>
       </c>
       <c r="E2" t="n">
-        <v>1207</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3895923808.758009</v>
+        <v>3958284043.137915</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.32579865</v>
+        <v>22.74239014</v>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2439137848.61445</v>
+        <v>2419237740.442198</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.97760921</v>
+        <v>13.89977272</v>
       </c>
       <c r="E4" t="n">
-        <v>306</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2150714229.62248</v>
+        <v>2165029216.066797</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.32478231</v>
+        <v>12.4392132</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1955703569.021117</v>
+        <v>1947780661.308562</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.20726335</v>
+        <v>11.19100783</v>
       </c>
       <c r="E6" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>878688702.7877141</v>
+        <v>884847982.5087212</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.03537236</v>
+        <v>5.08390955</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>176982833.7347319</v>
+        <v>177158587.8862599</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01420954</v>
+        <v>1.01786776</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20764842</v>
+        <v>0.20819066</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17450322245.40804</v>
+        <v>17404872655.3408</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E185"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4577,6 +4577,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="n">
+        <v>2165029216.066797</v>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>12.4392132</v>
+      </c>
+      <c r="E186" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="n">
+        <v>2419237740.442198</v>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>13.89977272</v>
+      </c>
+      <c r="E187" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="n">
+        <v>884847982.5087212</v>
+      </c>
+      <c r="D188" s="3" t="n">
+        <v>5.08390955</v>
+      </c>
+      <c r="E188" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="n">
+        <v>1947780661.308562</v>
+      </c>
+      <c r="D189" s="3" t="n">
+        <v>11.19100783</v>
+      </c>
+      <c r="E189" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="n">
+        <v>3958284043.137915</v>
+      </c>
+      <c r="D190" s="3" t="n">
+        <v>22.74239014</v>
+      </c>
+      <c r="E190" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="n">
+        <v>5816299104.73747</v>
+      </c>
+      <c r="D191" s="3" t="n">
+        <v>33.41764815</v>
+      </c>
+      <c r="E191" t="n">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="n">
+        <v>177158587.8862599</v>
+      </c>
+      <c r="D192" s="3" t="n">
+        <v>1.01786776</v>
+      </c>
+      <c r="E192" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D193" s="3" t="n">
+        <v>0.20819066</v>
+      </c>
+      <c r="E193" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5816299104.73747</v>
+        <v>5801157017.810042</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.41764815</v>
+        <v>33.36921988</v>
       </c>
       <c r="E2" t="n">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3958284043.137915</v>
+        <v>3931350083.82316</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.74239014</v>
+        <v>22.61377945</v>
       </c>
       <c r="E3" t="n">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2419237740.442198</v>
+        <v>2415534008.050455</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.89977272</v>
+        <v>13.89455331</v>
       </c>
       <c r="E4" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2165029216.066797</v>
+        <v>2163116965.048787</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.4392132</v>
+        <v>12.4426085</v>
       </c>
       <c r="E5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1947780661.308562</v>
+        <v>1973682842.416355</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.19100783</v>
+        <v>11.35295193</v>
       </c>
       <c r="E6" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>884847982.5087212</v>
+        <v>890504408.4990252</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.08390955</v>
+        <v>5.12232945</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>177158587.8862599</v>
+        <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01786776</v>
+        <v>0.99612589</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20819066</v>
+        <v>0.20843158</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17404872655.3408</v>
+        <v>17384754688.11355</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4745,6 +4745,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="n">
+        <v>2163116965.048787</v>
+      </c>
+      <c r="D194" s="3" t="n">
+        <v>12.4426085</v>
+      </c>
+      <c r="E194" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="n">
+        <v>2415534008.050455</v>
+      </c>
+      <c r="D195" s="3" t="n">
+        <v>13.89455331</v>
+      </c>
+      <c r="E195" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="n">
+        <v>890504408.4990252</v>
+      </c>
+      <c r="D196" s="3" t="n">
+        <v>5.12232945</v>
+      </c>
+      <c r="E196" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="n">
+        <v>1973682842.416355</v>
+      </c>
+      <c r="D197" s="3" t="n">
+        <v>11.35295193</v>
+      </c>
+      <c r="E197" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="n">
+        <v>3931350083.82316</v>
+      </c>
+      <c r="D198" s="3" t="n">
+        <v>22.61377945</v>
+      </c>
+      <c r="E198" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="n">
+        <v>5801157017.810042</v>
+      </c>
+      <c r="D199" s="3" t="n">
+        <v>33.36921988</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D200" s="3" t="n">
+        <v>0.99612589</v>
+      </c>
+      <c r="E200" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D201" s="3" t="n">
+        <v>0.20843158</v>
+      </c>
+      <c r="E201" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5801157017.810042</v>
+        <v>5827726659.77022</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.36921988</v>
+        <v>33.60141847</v>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3931350083.82316</v>
+        <v>3948139689.71734</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.61377945</v>
+        <v>22.76412427</v>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2415534008.050455</v>
+        <v>2392322565.545895</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.89455331</v>
+        <v>13.79361736</v>
       </c>
       <c r="E4" t="n">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2163116965.048787</v>
+        <v>2138550510.268667</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.4426085</v>
+        <v>12.33042228</v>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1973682842.416355</v>
+        <v>1936975801.566954</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.35295193</v>
+        <v>11.16818586</v>
       </c>
       <c r="E6" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>890504408.4990252</v>
+        <v>887913301.1683152</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12232945</v>
+        <v>5.11951712</v>
       </c>
       <c r="E7" t="n">
         <v>46</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>173174043.2128489</v>
+        <v>175828545.9129989</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.99612589</v>
+        <v>1.01378958</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20843158</v>
+        <v>0.20892506</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17384754688.11355</v>
+        <v>17343692393.20327</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4913,6 +4913,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="n">
+        <v>2138550510.268667</v>
+      </c>
+      <c r="D202" s="3" t="n">
+        <v>12.33042228</v>
+      </c>
+      <c r="E202" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="n">
+        <v>2392322565.545895</v>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>13.79361736</v>
+      </c>
+      <c r="E203" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="n">
+        <v>887913301.1683152</v>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>5.11951712</v>
+      </c>
+      <c r="E204" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="n">
+        <v>1936975801.566954</v>
+      </c>
+      <c r="D205" s="3" t="n">
+        <v>11.16818586</v>
+      </c>
+      <c r="E205" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="n">
+        <v>3948139689.71734</v>
+      </c>
+      <c r="D206" s="3" t="n">
+        <v>22.76412427</v>
+      </c>
+      <c r="E206" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="n">
+        <v>5827726659.77022</v>
+      </c>
+      <c r="D207" s="3" t="n">
+        <v>33.60141847</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="n">
+        <v>175828545.9129989</v>
+      </c>
+      <c r="D208" s="3" t="n">
+        <v>1.01378958</v>
+      </c>
+      <c r="E208" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D209" s="3" t="n">
+        <v>0.20892506</v>
+      </c>
+      <c r="E209" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5827726659.77022</v>
+        <v>5827655489.874527</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.60141847</v>
+        <v>33.7595089</v>
       </c>
       <c r="E2" t="n">
-        <v>1213</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3948139689.71734</v>
+        <v>3840057410.857652</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.76412427</v>
+        <v>22.24538711</v>
       </c>
       <c r="E3" t="n">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2392322565.545895</v>
+        <v>2407973937.723936</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.79361736</v>
+        <v>13.94935197</v>
       </c>
       <c r="E4" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2138550510.268667</v>
+        <v>2131441854.12513</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.33042228</v>
+        <v>12.34740632</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1936975801.566954</v>
+        <v>1960933269.167082</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.16818586</v>
+        <v>11.359653</v>
       </c>
       <c r="E6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>887913301.1683152</v>
+        <v>884792494.6508582</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.11951712</v>
+        <v>5.12558784</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175828545.9129989</v>
+        <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01378958</v>
+        <v>1.00319428</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20892506</v>
+        <v>0.20991059</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17343692393.20327</v>
+        <v>17262263818.86491</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E209"/>
+  <dimension ref="A1:E217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5081,6 +5081,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="n">
+        <v>2131441854.12513</v>
+      </c>
+      <c r="D210" s="3" t="n">
+        <v>12.34740632</v>
+      </c>
+      <c r="E210" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="n">
+        <v>2407973937.723936</v>
+      </c>
+      <c r="D211" s="3" t="n">
+        <v>13.94935197</v>
+      </c>
+      <c r="E211" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="n">
+        <v>884792494.6508582</v>
+      </c>
+      <c r="D212" s="3" t="n">
+        <v>5.12558784</v>
+      </c>
+      <c r="E212" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="n">
+        <v>1960933269.167082</v>
+      </c>
+      <c r="D213" s="3" t="n">
+        <v>11.359653</v>
+      </c>
+      <c r="E213" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="n">
+        <v>3840057410.857652</v>
+      </c>
+      <c r="D214" s="3" t="n">
+        <v>22.24538711</v>
+      </c>
+      <c r="E214" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="n">
+        <v>5827655489.874527</v>
+      </c>
+      <c r="D215" s="3" t="n">
+        <v>33.7595089</v>
+      </c>
+      <c r="E215" t="n">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D216" s="3" t="n">
+        <v>1.00319428</v>
+      </c>
+      <c r="E216" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D217" s="3" t="n">
+        <v>0.20991059</v>
+      </c>
+      <c r="E217" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5827655489.874527</v>
+        <v>5816914105.470725</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.7595089</v>
+        <v>33.59444472</v>
       </c>
       <c r="E2" t="n">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3840057410.857652</v>
+        <v>3905662846.268882</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.24538711</v>
+        <v>22.55638853</v>
       </c>
       <c r="E3" t="n">
         <v>227</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2407973937.723936</v>
+        <v>2424378286.716154</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.94935197</v>
+        <v>14.00152054</v>
       </c>
       <c r="E4" t="n">
-        <v>301</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2131441854.12513</v>
+        <v>2131749098.112009</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.34740632</v>
+        <v>12.31149815</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1960933269.167082</v>
+        <v>1945276729.373976</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.359653</v>
+        <v>11.23456361</v>
       </c>
       <c r="E6" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>884792494.6508582</v>
+        <v>881716738.5693132</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12558784</v>
+        <v>5.09218182</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00319428</v>
+        <v>1.00013267</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20991059</v>
+        <v>0.20926997</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17262263818.86491</v>
+        <v>17315107166.97679</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E217"/>
+  <dimension ref="A1:E225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5249,6 +5249,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="n">
+        <v>2131749098.112009</v>
+      </c>
+      <c r="D218" s="3" t="n">
+        <v>12.31149815</v>
+      </c>
+      <c r="E218" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="n">
+        <v>2424378286.716154</v>
+      </c>
+      <c r="D219" s="3" t="n">
+        <v>14.00152054</v>
+      </c>
+      <c r="E219" t="n">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="n">
+        <v>881716738.5693132</v>
+      </c>
+      <c r="D220" s="3" t="n">
+        <v>5.09218182</v>
+      </c>
+      <c r="E220" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="n">
+        <v>1945276729.373976</v>
+      </c>
+      <c r="D221" s="3" t="n">
+        <v>11.23456361</v>
+      </c>
+      <c r="E221" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="n">
+        <v>3905662846.268882</v>
+      </c>
+      <c r="D222" s="3" t="n">
+        <v>22.55638853</v>
+      </c>
+      <c r="E222" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="n">
+        <v>5816914105.470725</v>
+      </c>
+      <c r="D223" s="3" t="n">
+        <v>33.59444472</v>
+      </c>
+      <c r="E223" t="n">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D224" s="3" t="n">
+        <v>1.00013267</v>
+      </c>
+      <c r="E224" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D225" s="3" t="n">
+        <v>0.20926997</v>
+      </c>
+      <c r="E225" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5816914105.470725</v>
+        <v>5833449696.348156</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.59444472</v>
+        <v>33.79400228</v>
       </c>
       <c r="E2" t="n">
-        <v>1215</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3905662846.268882</v>
+        <v>3849223615.979109</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.55638853</v>
+        <v>22.29909889</v>
       </c>
       <c r="E3" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2424378286.716154</v>
+        <v>2407893582.376346</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.00152054</v>
+        <v>13.94926938</v>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2131749098.112009</v>
+        <v>2142272262.445588</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.31149815</v>
+        <v>12.41048736</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1945276729.373976</v>
+        <v>1929052886.50786</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.23456361</v>
+        <v>11.17527725</v>
       </c>
       <c r="E6" t="n">
         <v>131</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>881716738.5693132</v>
+        <v>897628817.7334822</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.09218182</v>
+        <v>5.20009118</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>173174043.2128489</v>
+        <v>166033787.9646789</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00013267</v>
+        <v>0.96185731</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20926997</v>
+        <v>0.20991635</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17315107166.97679</v>
+        <v>17261789968.6081</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E225"/>
+  <dimension ref="A1:E233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5417,6 +5417,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="n">
+        <v>2142272262.445588</v>
+      </c>
+      <c r="D226" s="3" t="n">
+        <v>12.41048736</v>
+      </c>
+      <c r="E226" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="n">
+        <v>2407893582.376346</v>
+      </c>
+      <c r="D227" s="3" t="n">
+        <v>13.94926938</v>
+      </c>
+      <c r="E227" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="n">
+        <v>897628817.7334822</v>
+      </c>
+      <c r="D228" s="3" t="n">
+        <v>5.20009118</v>
+      </c>
+      <c r="E228" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="n">
+        <v>1929052886.50786</v>
+      </c>
+      <c r="D229" s="3" t="n">
+        <v>11.17527725</v>
+      </c>
+      <c r="E229" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="n">
+        <v>3849223615.979109</v>
+      </c>
+      <c r="D230" s="3" t="n">
+        <v>22.29909889</v>
+      </c>
+      <c r="E230" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="n">
+        <v>5833449696.348156</v>
+      </c>
+      <c r="D231" s="3" t="n">
+        <v>33.79400228</v>
+      </c>
+      <c r="E231" t="n">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="n">
+        <v>166033787.9646789</v>
+      </c>
+      <c r="D232" s="3" t="n">
+        <v>0.96185731</v>
+      </c>
+      <c r="E232" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D233" s="3" t="n">
+        <v>0.20991635</v>
+      </c>
+      <c r="E233" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5833449696.348156</v>
+        <v>5830356329.431668</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.79400228</v>
+        <v>33.77373841</v>
       </c>
       <c r="E2" t="n">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3849223615.979109</v>
+        <v>3863156835.560662</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.29909889</v>
+        <v>22.37826319</v>
       </c>
       <c r="E3" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2407893582.376346</v>
+        <v>2415817211.957964</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.94926938</v>
+        <v>13.99420103</v>
       </c>
       <c r="E4" t="n">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2142272262.445588</v>
+        <v>2135782112.999039</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.41048736</v>
+        <v>12.37203051</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1929052886.50786</v>
+        <v>1926002280.038073</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.17527725</v>
+        <v>11.15683048</v>
       </c>
       <c r="E6" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>897628817.7334822</v>
+        <v>882463630.6473973</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.20009118</v>
+        <v>5.11188239</v>
       </c>
       <c r="E7" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>166033787.9646789</v>
+        <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.96185731</v>
+        <v>1.00315221</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20991635</v>
+        <v>0.20990178</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17261789968.6081</v>
+        <v>17262987763.10053</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E233"/>
+  <dimension ref="A1:E241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5585,6 +5585,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="n">
+        <v>2135782112.999039</v>
+      </c>
+      <c r="D234" s="3" t="n">
+        <v>12.37203051</v>
+      </c>
+      <c r="E234" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="n">
+        <v>2415817211.957964</v>
+      </c>
+      <c r="D235" s="3" t="n">
+        <v>13.99420103</v>
+      </c>
+      <c r="E235" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="n">
+        <v>882463630.6473973</v>
+      </c>
+      <c r="D236" s="3" t="n">
+        <v>5.11188239</v>
+      </c>
+      <c r="E236" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="n">
+        <v>1926002280.038073</v>
+      </c>
+      <c r="D237" s="3" t="n">
+        <v>11.15683048</v>
+      </c>
+      <c r="E237" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="n">
+        <v>3863156835.560662</v>
+      </c>
+      <c r="D238" s="3" t="n">
+        <v>22.37826319</v>
+      </c>
+      <c r="E238" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="n">
+        <v>5830356329.431668</v>
+      </c>
+      <c r="D239" s="3" t="n">
+        <v>33.77373841</v>
+      </c>
+      <c r="E239" t="n">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D240" s="3" t="n">
+        <v>1.00315221</v>
+      </c>
+      <c r="E240" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D241" s="3" t="n">
+        <v>0.20990178</v>
+      </c>
+      <c r="E241" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5830356329.431668</v>
+        <v>5818221209.027895</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.77373841</v>
+        <v>33.65282588</v>
       </c>
       <c r="E2" t="n">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3863156835.560662</v>
+        <v>3873516624.56909</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.37826319</v>
+        <v>22.40457621</v>
       </c>
       <c r="E3" t="n">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2415817211.957964</v>
+        <v>2420890387.527724</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.99420103</v>
+        <v>14.00252753</v>
       </c>
       <c r="E4" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2135782112.999039</v>
+        <v>2160312623.98809</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.37203051</v>
+        <v>12.49533525</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1926002280.038073</v>
+        <v>1921944625.606912</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.15683048</v>
+        <v>11.11660515</v>
       </c>
       <c r="E6" t="n">
         <v>130</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882463630.6473973</v>
+        <v>884658048.3376721</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.11188239</v>
+        <v>5.11689779</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00315221</v>
+        <v>1.00164564</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20990178</v>
+        <v>0.20958655</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17262987763.10053</v>
+        <v>17288952881.52311</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E241"/>
+  <dimension ref="A1:E249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5753,6 +5753,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="n">
+        <v>2160312623.98809</v>
+      </c>
+      <c r="D242" s="3" t="n">
+        <v>12.49533525</v>
+      </c>
+      <c r="E242" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="n">
+        <v>2420890387.527724</v>
+      </c>
+      <c r="D243" s="3" t="n">
+        <v>14.00252753</v>
+      </c>
+      <c r="E243" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="n">
+        <v>884658048.3376721</v>
+      </c>
+      <c r="D244" s="3" t="n">
+        <v>5.11689779</v>
+      </c>
+      <c r="E244" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="n">
+        <v>1921944625.606912</v>
+      </c>
+      <c r="D245" s="3" t="n">
+        <v>11.11660515</v>
+      </c>
+      <c r="E245" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="n">
+        <v>3873516624.56909</v>
+      </c>
+      <c r="D246" s="3" t="n">
+        <v>22.40457621</v>
+      </c>
+      <c r="E246" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="n">
+        <v>5818221209.027895</v>
+      </c>
+      <c r="D247" s="3" t="n">
+        <v>33.65282588</v>
+      </c>
+      <c r="E247" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D248" s="3" t="n">
+        <v>1.00164564</v>
+      </c>
+      <c r="E248" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D249" s="3" t="n">
+        <v>0.20958655</v>
+      </c>
+      <c r="E249" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5818221209.027895</v>
+        <v>5720822755.835001</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.65282588</v>
+        <v>33.06513461</v>
       </c>
       <c r="E2" t="n">
         <v>1219</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3873516624.56909</v>
+        <v>3987497598.666077</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.40457621</v>
+        <v>23.04688512</v>
       </c>
       <c r="E3" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2420890387.527724</v>
+        <v>2415705469.831027</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.00252753</v>
+        <v>13.96226206</v>
       </c>
       <c r="E4" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2160312623.98809</v>
+        <v>2146598483.901354</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.49533525</v>
+        <v>12.40688112</v>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1921944625.606912</v>
+        <v>1937041791.923738</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.11660515</v>
+        <v>11.19568816</v>
       </c>
       <c r="E6" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>884658048.3376721</v>
+        <v>884601436.1515982</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.11689779</v>
+        <v>5.11280751</v>
       </c>
       <c r="E7" t="n">
         <v>45</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00164564</v>
+        <v>1.00090901</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20958655</v>
+        <v>0.20943241</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17288952881.52311</v>
+        <v>17301676898.77452</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E249"/>
+  <dimension ref="A1:E257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5921,6 +5921,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="n">
+        <v>2146598483.901354</v>
+      </c>
+      <c r="D250" s="3" t="n">
+        <v>12.40688112</v>
+      </c>
+      <c r="E250" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="n">
+        <v>2415705469.831027</v>
+      </c>
+      <c r="D251" s="3" t="n">
+        <v>13.96226206</v>
+      </c>
+      <c r="E251" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="n">
+        <v>884601436.1515982</v>
+      </c>
+      <c r="D252" s="3" t="n">
+        <v>5.11280751</v>
+      </c>
+      <c r="E252" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="n">
+        <v>1937041791.923738</v>
+      </c>
+      <c r="D253" s="3" t="n">
+        <v>11.19568816</v>
+      </c>
+      <c r="E253" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="n">
+        <v>3987497598.666077</v>
+      </c>
+      <c r="D254" s="3" t="n">
+        <v>23.04688512</v>
+      </c>
+      <c r="E254" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="n">
+        <v>5720822755.835001</v>
+      </c>
+      <c r="D255" s="3" t="n">
+        <v>33.06513461</v>
+      </c>
+      <c r="E255" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D256" s="3" t="n">
+        <v>1.00090901</v>
+      </c>
+      <c r="E256" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D257" s="3" t="n">
+        <v>0.20943241</v>
+      </c>
+      <c r="E257" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5720822755.835001</v>
+        <v>5818988555.490482</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.06513461</v>
+        <v>33.63123146</v>
       </c>
       <c r="E2" t="n">
-        <v>1219</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3987497598.666077</v>
+        <v>3887013583.827204</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>23.04688512</v>
+        <v>22.46525358</v>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2415705469.831027</v>
+        <v>2420267340.616417</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.96226206</v>
+        <v>13.9880961</v>
       </c>
       <c r="E4" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2146598483.901354</v>
+        <v>2132658214.279495</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.40688112</v>
+        <v>12.32584002</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1937041791.923738</v>
+        <v>1942915773.337785</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.19568816</v>
+        <v>11.22921096</v>
       </c>
       <c r="E6" t="n">
         <v>131</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>884601436.1515982</v>
+        <v>884562617.6767291</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.11280751</v>
+        <v>5.11238849</v>
       </c>
       <c r="E7" t="n">
         <v>45</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>173174043.2128489</v>
+        <v>182200673.6729709</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00090901</v>
+        <v>1.05304091</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>36235319.252875</v>
+        <v>33728908.648298</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20943241</v>
+        <v>0.19493847</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17301676898.77452</v>
+        <v>17302335667.54938</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E257"/>
+  <dimension ref="A1:E265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6089,6 +6089,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="n">
+        <v>2132658214.279495</v>
+      </c>
+      <c r="D258" s="3" t="n">
+        <v>12.32584002</v>
+      </c>
+      <c r="E258" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="n">
+        <v>2420267340.616417</v>
+      </c>
+      <c r="D259" s="3" t="n">
+        <v>13.9880961</v>
+      </c>
+      <c r="E259" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="n">
+        <v>884562617.6767291</v>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>5.11238849</v>
+      </c>
+      <c r="E260" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="n">
+        <v>1942915773.337785</v>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>11.22921096</v>
+      </c>
+      <c r="E261" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="n">
+        <v>3887013583.827204</v>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>22.46525358</v>
+      </c>
+      <c r="E262" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="n">
+        <v>5818988555.490482</v>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>33.63123146</v>
+      </c>
+      <c r="E263" t="n">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="n">
+        <v>182200673.6729709</v>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>1.05304091</v>
+      </c>
+      <c r="E264" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="n">
+        <v>33728908.648298</v>
+      </c>
+      <c r="D265" s="3" t="n">
+        <v>0.19493847</v>
+      </c>
+      <c r="E265" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5818988555.490482</v>
+        <v>5817364799.476451</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.63123146</v>
+        <v>33.6324207</v>
       </c>
       <c r="E2" t="n">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3887013583.827204</v>
+        <v>3873139045.781398</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.46525358</v>
+        <v>22.39210473</v>
       </c>
       <c r="E3" t="n">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2420267340.616417</v>
+        <v>2413375322.829756</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.9880961</v>
+        <v>13.95264986</v>
       </c>
       <c r="E4" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2132658214.279495</v>
+        <v>2139239754.974089</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.32584002</v>
+        <v>12.36776683</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1942915773.337785</v>
+        <v>1958986109.658107</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.22921096</v>
+        <v>11.32565126</v>
       </c>
       <c r="E6" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>884562617.6767291</v>
+        <v>885381511.0777022</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.11238849</v>
+        <v>5.11873064</v>
       </c>
       <c r="E7" t="n">
         <v>45</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>182200673.6729709</v>
+        <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.05304091</v>
+        <v>1.00118567</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>33728908.648298</v>
+        <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.19493847</v>
+        <v>0.2094903</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17302335667.54938</v>
+        <v>17296895906.26323</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E265"/>
+  <dimension ref="A1:E273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6257,6 +6257,174 @@
         <v>6</v>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="n">
+        <v>2139239754.974089</v>
+      </c>
+      <c r="D266" s="3" t="n">
+        <v>12.36776683</v>
+      </c>
+      <c r="E266" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="n">
+        <v>2413375322.829756</v>
+      </c>
+      <c r="D267" s="3" t="n">
+        <v>13.95264986</v>
+      </c>
+      <c r="E267" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="n">
+        <v>885381511.0777022</v>
+      </c>
+      <c r="D268" s="3" t="n">
+        <v>5.11873064</v>
+      </c>
+      <c r="E268" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="n">
+        <v>1958986109.658107</v>
+      </c>
+      <c r="D269" s="3" t="n">
+        <v>11.32565126</v>
+      </c>
+      <c r="E269" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="n">
+        <v>3873139045.781398</v>
+      </c>
+      <c r="D270" s="3" t="n">
+        <v>22.39210473</v>
+      </c>
+      <c r="E270" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="n">
+        <v>5817364799.476451</v>
+      </c>
+      <c r="D271" s="3" t="n">
+        <v>33.6324207</v>
+      </c>
+      <c r="E271" t="n">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D272" s="3" t="n">
+        <v>1.00118567</v>
+      </c>
+      <c r="E272" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D273" s="3" t="n">
+        <v>0.2094903</v>
+      </c>
+      <c r="E273" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5817364799.476451</v>
+        <v>5728106844.324675</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.6324207</v>
+        <v>33.12320932</v>
       </c>
       <c r="E2" t="n">
-        <v>1215</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3873139045.781398</v>
+        <v>3974555840.549272</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.39210473</v>
+        <v>22.98316855</v>
       </c>
       <c r="E3" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2413375322.829756</v>
+        <v>2407994004.60226</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.95264986</v>
+        <v>13.92440672</v>
       </c>
       <c r="E4" t="n">
         <v>302</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2139239754.974089</v>
+        <v>2141802720.360499</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.36776683</v>
+        <v>12.38513557</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1958986109.658107</v>
+        <v>1935312428.810368</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.32565126</v>
+        <v>11.1910899</v>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>885381511.0777022</v>
+        <v>890436578.7266572</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.11873064</v>
+        <v>5.14901659</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>173174043.2128489</v>
+        <v>178889132.5383159</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00118567</v>
+        <v>1.03443988</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.2094903</v>
+        <v>0.20953346</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17296895906.26323</v>
+        <v>17293332869.16492</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E273"/>
+  <dimension ref="A1:E281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6425,6 +6425,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="n">
+        <v>2141802720.360499</v>
+      </c>
+      <c r="D274" s="3" t="n">
+        <v>12.38513557</v>
+      </c>
+      <c r="E274" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="n">
+        <v>2407994004.60226</v>
+      </c>
+      <c r="D275" s="3" t="n">
+        <v>13.92440672</v>
+      </c>
+      <c r="E275" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="n">
+        <v>890436578.7266572</v>
+      </c>
+      <c r="D276" s="3" t="n">
+        <v>5.14901659</v>
+      </c>
+      <c r="E276" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="n">
+        <v>1935312428.810368</v>
+      </c>
+      <c r="D277" s="3" t="n">
+        <v>11.1910899</v>
+      </c>
+      <c r="E277" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="n">
+        <v>3974555840.549272</v>
+      </c>
+      <c r="D278" s="3" t="n">
+        <v>22.98316855</v>
+      </c>
+      <c r="E278" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="n">
+        <v>5728106844.324675</v>
+      </c>
+      <c r="D279" s="3" t="n">
+        <v>33.12320932</v>
+      </c>
+      <c r="E279" t="n">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="n">
+        <v>178889132.5383159</v>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>1.03443988</v>
+      </c>
+      <c r="E280" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D281" s="3" t="n">
+        <v>0.20953346</v>
+      </c>
+      <c r="E281" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5728106844.324675</v>
+        <v>5707235594.159877</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.12320932</v>
+        <v>32.9899633</v>
       </c>
       <c r="E2" t="n">
-        <v>1217</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3974555840.549272</v>
+        <v>3976778678.418463</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.98316855</v>
+        <v>22.98727299</v>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2407994004.60226</v>
+        <v>2417065175.838721</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.92440672</v>
+        <v>13.97154369</v>
       </c>
       <c r="E4" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2141802720.360499</v>
+        <v>2148675744.853878</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.38513557</v>
+        <v>12.42015207</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1935312428.810368</v>
+        <v>1951932453.37772</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.1910899</v>
+        <v>11.28290202</v>
       </c>
       <c r="E6" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>890436578.7266572</v>
+        <v>884590890.1886071</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.14901659</v>
+        <v>5.11326728</v>
       </c>
       <c r="E7" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>178889132.5383159</v>
+        <v>177401099.1998569</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.03443988</v>
+        <v>1.02544492</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20953346</v>
+        <v>0.20945374</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17293332869.16492</v>
+        <v>17299914955.29</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E281"/>
+  <dimension ref="A1:E289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6593,6 +6593,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="n">
+        <v>2148675744.853878</v>
+      </c>
+      <c r="D282" s="3" t="n">
+        <v>12.42015207</v>
+      </c>
+      <c r="E282" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="n">
+        <v>2417065175.838721</v>
+      </c>
+      <c r="D283" s="3" t="n">
+        <v>13.97154369</v>
+      </c>
+      <c r="E283" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="n">
+        <v>884590890.1886071</v>
+      </c>
+      <c r="D284" s="3" t="n">
+        <v>5.11326728</v>
+      </c>
+      <c r="E284" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="n">
+        <v>1951932453.37772</v>
+      </c>
+      <c r="D285" s="3" t="n">
+        <v>11.28290202</v>
+      </c>
+      <c r="E285" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="n">
+        <v>3976778678.418463</v>
+      </c>
+      <c r="D286" s="3" t="n">
+        <v>22.98727299</v>
+      </c>
+      <c r="E286" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="n">
+        <v>5707235594.159877</v>
+      </c>
+      <c r="D287" s="3" t="n">
+        <v>32.9899633</v>
+      </c>
+      <c r="E287" t="n">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="n">
+        <v>177401099.1998569</v>
+      </c>
+      <c r="D288" s="3" t="n">
+        <v>1.02544492</v>
+      </c>
+      <c r="E288" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D289" s="3" t="n">
+        <v>0.20945374</v>
+      </c>
+      <c r="E289" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5707235594.159877</v>
+        <v>5791011136.668227</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>32.9899633</v>
+        <v>33.54607007</v>
       </c>
       <c r="E2" t="n">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3976778678.418463</v>
+        <v>3837035096.002688</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.98727299</v>
+        <v>22.22711115</v>
       </c>
       <c r="E3" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2417065175.838721</v>
+        <v>2409041261.185152</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.97154369</v>
+        <v>13.95505293</v>
       </c>
       <c r="E4" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2148675744.853878</v>
+        <v>2155659718.268834</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.42015207</v>
+        <v>12.48726867</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1951932453.37772</v>
+        <v>1969415404.139005</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.28290202</v>
+        <v>11.4083958</v>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>884590890.1886071</v>
+        <v>891288096.0187991</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.11326728</v>
+        <v>5.16303841</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>177401099.1998569</v>
+        <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02544492</v>
+        <v>1.00315963</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20945374</v>
+        <v>0.20990334</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17299914955.29</v>
+        <v>17262860074.74843</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E289"/>
+  <dimension ref="A1:E297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6761,6 +6761,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="n">
+        <v>2155659718.268834</v>
+      </c>
+      <c r="D290" s="3" t="n">
+        <v>12.48726867</v>
+      </c>
+      <c r="E290" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="n">
+        <v>2409041261.185152</v>
+      </c>
+      <c r="D291" s="3" t="n">
+        <v>13.95505293</v>
+      </c>
+      <c r="E291" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="n">
+        <v>891288096.0187991</v>
+      </c>
+      <c r="D292" s="3" t="n">
+        <v>5.16303841</v>
+      </c>
+      <c r="E292" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="n">
+        <v>1969415404.139005</v>
+      </c>
+      <c r="D293" s="3" t="n">
+        <v>11.4083958</v>
+      </c>
+      <c r="E293" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="n">
+        <v>3837035096.002688</v>
+      </c>
+      <c r="D294" s="3" t="n">
+        <v>22.22711115</v>
+      </c>
+      <c r="E294" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="n">
+        <v>5791011136.668227</v>
+      </c>
+      <c r="D295" s="3" t="n">
+        <v>33.54607007</v>
+      </c>
+      <c r="E295" t="n">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D296" s="3" t="n">
+        <v>1.00315963</v>
+      </c>
+      <c r="E296" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D297" s="3" t="n">
+        <v>0.20990334</v>
+      </c>
+      <c r="E297" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5791011136.668227</v>
+        <v>5793327636.379858</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.54607007</v>
+        <v>33.5542136</v>
       </c>
       <c r="E2" t="n">
-        <v>1210</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3837035096.002688</v>
+        <v>3903938954.065184</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.22711115</v>
+        <v>22.61111571</v>
       </c>
       <c r="E3" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2409041261.185152</v>
+        <v>2391920609.063651</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.95505293</v>
+        <v>13.85369861</v>
       </c>
       <c r="E4" t="n">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2155659718.268834</v>
+        <v>2139458140.506424</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.48726867</v>
+        <v>12.39146824</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1969415404.139005</v>
+        <v>1926434247.460227</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.4083958</v>
+        <v>11.15766107</v>
       </c>
       <c r="E6" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>891288096.0187991</v>
+        <v>895370131.5995281</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.16303841</v>
+        <v>5.18586942</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>173174043.2128489</v>
+        <v>178889132.5383159</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00315963</v>
+        <v>1.036103</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20990334</v>
+        <v>0.20987034</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17262860074.74843</v>
+        <v>17265574170.86606</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E297"/>
+  <dimension ref="A1:E305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6929,6 +6929,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="n">
+        <v>2139458140.506424</v>
+      </c>
+      <c r="D298" s="3" t="n">
+        <v>12.39146824</v>
+      </c>
+      <c r="E298" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="n">
+        <v>2391920609.063651</v>
+      </c>
+      <c r="D299" s="3" t="n">
+        <v>13.85369861</v>
+      </c>
+      <c r="E299" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="n">
+        <v>895370131.5995281</v>
+      </c>
+      <c r="D300" s="3" t="n">
+        <v>5.18586942</v>
+      </c>
+      <c r="E300" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="n">
+        <v>1926434247.460227</v>
+      </c>
+      <c r="D301" s="3" t="n">
+        <v>11.15766107</v>
+      </c>
+      <c r="E301" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="n">
+        <v>3903938954.065184</v>
+      </c>
+      <c r="D302" s="3" t="n">
+        <v>22.61111571</v>
+      </c>
+      <c r="E302" t="n">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="n">
+        <v>5793327636.379858</v>
+      </c>
+      <c r="D303" s="3" t="n">
+        <v>33.5542136</v>
+      </c>
+      <c r="E303" t="n">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="n">
+        <v>178889132.5383159</v>
+      </c>
+      <c r="D304" s="3" t="n">
+        <v>1.036103</v>
+      </c>
+      <c r="E304" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D305" s="3" t="n">
+        <v>0.20987034</v>
+      </c>
+      <c r="E305" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5793327636.379858</v>
+        <v>5766368713.481582</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.5542136</v>
+        <v>33.41120593</v>
       </c>
       <c r="E2" t="n">
-        <v>1214</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3903938954.065184</v>
+        <v>3876454100.981374</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.61111571</v>
+        <v>22.46075696</v>
       </c>
       <c r="E3" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2391920609.063651</v>
+        <v>2420151410.376505</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.85369861</v>
+        <v>14.02272057</v>
       </c>
       <c r="E4" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2139458140.506424</v>
+        <v>2154567725.330556</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.39146824</v>
+        <v>12.48388883</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1926434247.460227</v>
+        <v>1947283768.866755</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.15766107</v>
+        <v>11.28285447</v>
       </c>
       <c r="E6" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>895370131.5995281</v>
+        <v>884551465.2233211</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.18586942</v>
+        <v>5.12522397</v>
       </c>
       <c r="E7" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>178889132.5383159</v>
+        <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.036103</v>
+        <v>1.0033964</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20987034</v>
+        <v>0.20995288</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17265574170.86606</v>
+        <v>17258786546.72582</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E305"/>
+  <dimension ref="A1:E313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7097,6 +7097,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="n">
+        <v>2154567725.330556</v>
+      </c>
+      <c r="D306" s="3" t="n">
+        <v>12.48388883</v>
+      </c>
+      <c r="E306" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="n">
+        <v>2420151410.376505</v>
+      </c>
+      <c r="D307" s="3" t="n">
+        <v>14.02272057</v>
+      </c>
+      <c r="E307" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="n">
+        <v>884551465.2233211</v>
+      </c>
+      <c r="D308" s="3" t="n">
+        <v>5.12522397</v>
+      </c>
+      <c r="E308" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="n">
+        <v>1947283768.866755</v>
+      </c>
+      <c r="D309" s="3" t="n">
+        <v>11.28285447</v>
+      </c>
+      <c r="E309" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="n">
+        <v>3876454100.981374</v>
+      </c>
+      <c r="D310" s="3" t="n">
+        <v>22.46075696</v>
+      </c>
+      <c r="E310" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="n">
+        <v>5766368713.481582</v>
+      </c>
+      <c r="D311" s="3" t="n">
+        <v>33.41120593</v>
+      </c>
+      <c r="E311" t="n">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D312" s="3" t="n">
+        <v>1.0033964</v>
+      </c>
+      <c r="E312" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D313" s="3" t="n">
+        <v>0.20995288</v>
+      </c>
+      <c r="E313" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5766368713.481582</v>
+        <v>5810291155.668639</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.41120593</v>
+        <v>33.6727568</v>
       </c>
       <c r="E2" t="n">
-        <v>1208</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3876454100.981374</v>
+        <v>3879886163.904713</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.46075696</v>
+        <v>22.48535568</v>
       </c>
       <c r="E3" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2420151410.376505</v>
+        <v>2397930879.238109</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.02272057</v>
+        <v>13.8968842</v>
       </c>
       <c r="E4" t="n">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2154567725.330556</v>
+        <v>2144611264.413765</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.48388883</v>
+        <v>12.42880462</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1947283768.866755</v>
+        <v>1938838685.416232</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.28285447</v>
+        <v>11.23627746</v>
       </c>
       <c r="E6" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>884551465.2233211</v>
+        <v>876856175.8951762</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12522397</v>
+        <v>5.08170141</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>173174043.2128489</v>
+        <v>170519540.5126989</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.0033964</v>
+        <v>0.98822294</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20995288</v>
+        <v>0.20999689</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17258786546.72582</v>
+        <v>17255169184.30221</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E313"/>
+  <dimension ref="A1:E321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7265,6 +7265,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="n">
+        <v>2144611264.413765</v>
+      </c>
+      <c r="D314" s="3" t="n">
+        <v>12.42880462</v>
+      </c>
+      <c r="E314" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="n">
+        <v>2397930879.238109</v>
+      </c>
+      <c r="D315" s="3" t="n">
+        <v>13.8968842</v>
+      </c>
+      <c r="E315" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="n">
+        <v>876856175.8951762</v>
+      </c>
+      <c r="D316" s="3" t="n">
+        <v>5.08170141</v>
+      </c>
+      <c r="E316" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="n">
+        <v>1938838685.416232</v>
+      </c>
+      <c r="D317" s="3" t="n">
+        <v>11.23627746</v>
+      </c>
+      <c r="E317" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="n">
+        <v>3879886163.904713</v>
+      </c>
+      <c r="D318" s="3" t="n">
+        <v>22.48535568</v>
+      </c>
+      <c r="E318" t="n">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="n">
+        <v>5810291155.668639</v>
+      </c>
+      <c r="D319" s="3" t="n">
+        <v>33.6727568</v>
+      </c>
+      <c r="E319" t="n">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="n">
+        <v>170519540.5126989</v>
+      </c>
+      <c r="D320" s="3" t="n">
+        <v>0.98822294</v>
+      </c>
+      <c r="E320" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D321" s="3" t="n">
+        <v>0.20999689</v>
+      </c>
+      <c r="E321" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5810291155.668639</v>
+        <v>5858219262.302409</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.6727568</v>
+        <v>33.94671821</v>
       </c>
       <c r="E2" t="n">
-        <v>1218</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3879886163.904713</v>
+        <v>3867447770.811736</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.48535568</v>
+        <v>22.41076235</v>
       </c>
       <c r="E3" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2397930879.238109</v>
+        <v>2415645097.592425</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.8968842</v>
+        <v>13.99797784</v>
       </c>
       <c r="E4" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2144611264.413765</v>
+        <v>2124073480.61378</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.42880462</v>
+        <v>12.30840306</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1938838685.416232</v>
+        <v>1913628738.925807</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.23627746</v>
+        <v>11.0889355</v>
       </c>
       <c r="E6" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>876856175.8951762</v>
+        <v>871331242.6922672</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.08170141</v>
+        <v>5.04911729</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>170519540.5126989</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.98822294</v>
+        <v>0.98811235</v>
       </c>
       <c r="E8" t="n">
         <v>20</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20999689</v>
+        <v>0.20997339</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17255169184.30221</v>
+        <v>17257100452.704</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E321"/>
+  <dimension ref="A1:E329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7433,6 +7433,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="n">
+        <v>2124073480.61378</v>
+      </c>
+      <c r="D322" s="3" t="n">
+        <v>12.30840306</v>
+      </c>
+      <c r="E322" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="n">
+        <v>2415645097.592425</v>
+      </c>
+      <c r="D323" s="3" t="n">
+        <v>13.99797784</v>
+      </c>
+      <c r="E323" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="n">
+        <v>871331242.6922672</v>
+      </c>
+      <c r="D324" s="3" t="n">
+        <v>5.04911729</v>
+      </c>
+      <c r="E324" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="n">
+        <v>1913628738.925807</v>
+      </c>
+      <c r="D325" s="3" t="n">
+        <v>11.0889355</v>
+      </c>
+      <c r="E325" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="n">
+        <v>3867447770.811736</v>
+      </c>
+      <c r="D326" s="3" t="n">
+        <v>22.41076235</v>
+      </c>
+      <c r="E326" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="n">
+        <v>5858219262.302409</v>
+      </c>
+      <c r="D327" s="3" t="n">
+        <v>33.94671821</v>
+      </c>
+      <c r="E327" t="n">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="n">
+        <v>170519540.5126989</v>
+      </c>
+      <c r="D328" s="3" t="n">
+        <v>0.98811235</v>
+      </c>
+      <c r="E328" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D329" s="3" t="n">
+        <v>0.20997339</v>
+      </c>
+      <c r="E329" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5858219262.302409</v>
+        <v>5831377029.867583</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.94671821</v>
+        <v>33.80140881</v>
       </c>
       <c r="E2" t="n">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3867447770.811736</v>
+        <v>3858363699.591795</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.41076235</v>
+        <v>22.36489393</v>
       </c>
       <c r="E3" t="n">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2415645097.592425</v>
+        <v>2404866947.324762</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.99797784</v>
+        <v>13.93974192</v>
       </c>
       <c r="E4" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2124073480.61378</v>
+        <v>2132972142.257311</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.30840306</v>
+        <v>12.36371152</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1913628738.925807</v>
+        <v>1937730386.529161</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.0889355</v>
+        <v>11.23199831</v>
       </c>
       <c r="E6" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>871331242.6922672</v>
+        <v>878618678.5354681</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.04911729</v>
+        <v>5.09288784</v>
       </c>
       <c r="E7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>170519540.5126989</v>
+        <v>174217899.7319289</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.98811235</v>
+        <v>1.00984903</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>36235319.252875</v>
+        <v>33728908.648298</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20997339</v>
+        <v>0.19550865</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17257100452.704</v>
+        <v>17251875692.48631</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E329"/>
+  <dimension ref="A1:E337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7601,6 +7601,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="n">
+        <v>2132972142.257311</v>
+      </c>
+      <c r="D330" s="3" t="n">
+        <v>12.36371152</v>
+      </c>
+      <c r="E330" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="n">
+        <v>2404866947.324762</v>
+      </c>
+      <c r="D331" s="3" t="n">
+        <v>13.93974192</v>
+      </c>
+      <c r="E331" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="n">
+        <v>878618678.5354681</v>
+      </c>
+      <c r="D332" s="3" t="n">
+        <v>5.09288784</v>
+      </c>
+      <c r="E332" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="n">
+        <v>1937730386.529161</v>
+      </c>
+      <c r="D333" s="3" t="n">
+        <v>11.23199831</v>
+      </c>
+      <c r="E333" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="n">
+        <v>3858363699.591795</v>
+      </c>
+      <c r="D334" s="3" t="n">
+        <v>22.36489393</v>
+      </c>
+      <c r="E334" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="n">
+        <v>5831377029.867583</v>
+      </c>
+      <c r="D335" s="3" t="n">
+        <v>33.80140881</v>
+      </c>
+      <c r="E335" t="n">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="n">
+        <v>174217899.7319289</v>
+      </c>
+      <c r="D336" s="3" t="n">
+        <v>1.00984903</v>
+      </c>
+      <c r="E336" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="n">
+        <v>33728908.648298</v>
+      </c>
+      <c r="D337" s="3" t="n">
+        <v>0.19550865</v>
+      </c>
+      <c r="E337" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5831377029.867583</v>
+        <v>5816032632.55343</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.80140881</v>
+        <v>33.72993335</v>
       </c>
       <c r="E2" t="n">
-        <v>1227</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3858363699.591795</v>
+        <v>3829256913.730375</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.36489393</v>
+        <v>22.20767809</v>
       </c>
       <c r="E3" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2404866947.324762</v>
+        <v>2406151982.029045</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.93974192</v>
+        <v>13.95441723</v>
       </c>
       <c r="E4" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2132972142.257311</v>
+        <v>2164539755.844994</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.36371152</v>
+        <v>12.55319327</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1937730386.529161</v>
+        <v>1939001264.519664</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.23199831</v>
+        <v>11.24518852</v>
       </c>
       <c r="E6" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>878618678.5354681</v>
+        <v>880012017.0119941</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.09288784</v>
+        <v>5.10360731</v>
       </c>
       <c r="E7" t="n">
         <v>43</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>174217899.7319289</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00984903</v>
+        <v>1.01037228</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>33728908.648298</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.19550865</v>
+        <v>0.19560995</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17251875692.48631</v>
+        <v>17242941374.06973</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E337"/>
+  <dimension ref="A1:E345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7769,6 +7769,174 @@
         <v>6</v>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="n">
+        <v>2164539755.844994</v>
+      </c>
+      <c r="D338" s="3" t="n">
+        <v>12.55319327</v>
+      </c>
+      <c r="E338" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="n">
+        <v>2406151982.029045</v>
+      </c>
+      <c r="D339" s="3" t="n">
+        <v>13.95441723</v>
+      </c>
+      <c r="E339" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="n">
+        <v>880012017.0119941</v>
+      </c>
+      <c r="D340" s="3" t="n">
+        <v>5.10360731</v>
+      </c>
+      <c r="E340" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="n">
+        <v>1939001264.519664</v>
+      </c>
+      <c r="D341" s="3" t="n">
+        <v>11.24518852</v>
+      </c>
+      <c r="E341" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="n">
+        <v>3829256913.730375</v>
+      </c>
+      <c r="D342" s="3" t="n">
+        <v>22.20767809</v>
+      </c>
+      <c r="E342" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="n">
+        <v>5816032632.55343</v>
+      </c>
+      <c r="D343" s="3" t="n">
+        <v>33.72993335</v>
+      </c>
+      <c r="E343" t="n">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="n">
+        <v>174217899.7319289</v>
+      </c>
+      <c r="D344" s="3" t="n">
+        <v>1.01037228</v>
+      </c>
+      <c r="E344" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="n">
+        <v>33728908.648298</v>
+      </c>
+      <c r="D345" s="3" t="n">
+        <v>0.19560995</v>
+      </c>
+      <c r="E345" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5816032632.55343</v>
+        <v>5791381120.264837</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.72993335</v>
+        <v>33.59200831</v>
       </c>
       <c r="E2" t="n">
-        <v>1223</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3829256913.730375</v>
+        <v>3855485355.590838</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.20767809</v>
+        <v>22.36314507</v>
       </c>
       <c r="E3" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2406151982.029045</v>
+        <v>2414749102.425952</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.95441723</v>
+        <v>14.00637779</v>
       </c>
       <c r="E4" t="n">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2164539755.844994</v>
+        <v>2165623975.717546</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.55319327</v>
+        <v>12.56136612</v>
       </c>
       <c r="E5" t="n">
         <v>49</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1939001264.519664</v>
+        <v>1919938102.543499</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.24518852</v>
+        <v>11.1363033</v>
       </c>
       <c r="E6" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>880012017.0119941</v>
+        <v>886273305.8586702</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.10360731</v>
+        <v>5.14069091</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>174217899.7319289</v>
+        <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01037228</v>
+        <v>1.00446919</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>33728908.648298</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.19560995</v>
+        <v>0.19563931</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17242941374.06973</v>
+        <v>17240353914.26249</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E345"/>
+  <dimension ref="A1:E353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7937,6 +7937,174 @@
         <v>6</v>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="n">
+        <v>2165623975.717546</v>
+      </c>
+      <c r="D346" s="3" t="n">
+        <v>12.56136612</v>
+      </c>
+      <c r="E346" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="n">
+        <v>2414749102.425952</v>
+      </c>
+      <c r="D347" s="3" t="n">
+        <v>14.00637779</v>
+      </c>
+      <c r="E347" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="n">
+        <v>886273305.8586702</v>
+      </c>
+      <c r="D348" s="3" t="n">
+        <v>5.14069091</v>
+      </c>
+      <c r="E348" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="n">
+        <v>1919938102.543499</v>
+      </c>
+      <c r="D349" s="3" t="n">
+        <v>11.1363033</v>
+      </c>
+      <c r="E349" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="n">
+        <v>3855485355.590838</v>
+      </c>
+      <c r="D350" s="3" t="n">
+        <v>22.36314507</v>
+      </c>
+      <c r="E350" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="n">
+        <v>5791381120.264837</v>
+      </c>
+      <c r="D351" s="3" t="n">
+        <v>33.59200831</v>
+      </c>
+      <c r="E351" t="n">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D352" s="3" t="n">
+        <v>1.00446919</v>
+      </c>
+      <c r="E352" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="n">
+        <v>33728908.648298</v>
+      </c>
+      <c r="D353" s="3" t="n">
+        <v>0.19563931</v>
+      </c>
+      <c r="E353" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5791381120.264837</v>
+        <v>5863078365.165998</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.59200831</v>
+        <v>33.97362865</v>
       </c>
       <c r="E2" t="n">
-        <v>1212</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3855485355.590838</v>
+        <v>3819136709.60262</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.36314507</v>
+        <v>22.13000139</v>
       </c>
       <c r="E3" t="n">
         <v>229</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2414749102.425952</v>
+        <v>2378611434.820736</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.00637779</v>
+        <v>13.78287251</v>
       </c>
       <c r="E4" t="n">
-        <v>306</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2165623975.717546</v>
+        <v>2155422870.124498</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.56136612</v>
+        <v>12.48960557</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1919938102.543499</v>
+        <v>1932651373.836447</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.1363033</v>
+        <v>11.19875533</v>
       </c>
       <c r="E6" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>886273305.8586702</v>
+        <v>890638595.2895253</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.14069091</v>
+        <v>5.16080854</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>173174043.2128489</v>
+        <v>180671887.9731569</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00446919</v>
+        <v>1.0469039</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>33728908.648298</v>
+        <v>37522474.912046</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.19563931</v>
+        <v>0.21742412</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17240353914.26249</v>
+        <v>17257733711.72503</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E353"/>
+  <dimension ref="A1:E361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8105,6 +8105,174 @@
         <v>6</v>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="n">
+        <v>2155422870.124498</v>
+      </c>
+      <c r="D354" s="3" t="n">
+        <v>12.48960557</v>
+      </c>
+      <c r="E354" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="n">
+        <v>2378611434.820736</v>
+      </c>
+      <c r="D355" s="3" t="n">
+        <v>13.78287251</v>
+      </c>
+      <c r="E355" t="n">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="n">
+        <v>890638595.2895253</v>
+      </c>
+      <c r="D356" s="3" t="n">
+        <v>5.16080854</v>
+      </c>
+      <c r="E356" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="n">
+        <v>1932651373.836447</v>
+      </c>
+      <c r="D357" s="3" t="n">
+        <v>11.19875533</v>
+      </c>
+      <c r="E357" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="n">
+        <v>3819136709.60262</v>
+      </c>
+      <c r="D358" s="3" t="n">
+        <v>22.13000139</v>
+      </c>
+      <c r="E358" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="n">
+        <v>5863078365.165998</v>
+      </c>
+      <c r="D359" s="3" t="n">
+        <v>33.97362865</v>
+      </c>
+      <c r="E359" t="n">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="n">
+        <v>180671887.9731569</v>
+      </c>
+      <c r="D360" s="3" t="n">
+        <v>1.0469039</v>
+      </c>
+      <c r="E360" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="n">
+        <v>37522474.912046</v>
+      </c>
+      <c r="D361" s="3" t="n">
+        <v>0.21742412</v>
+      </c>
+      <c r="E361" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5863078365.165998</v>
+        <v>5869939039.959793</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.97362865</v>
+        <v>33.97790324</v>
       </c>
       <c r="E2" t="n">
-        <v>1221</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3819136709.60262</v>
+        <v>3845703323.982821</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.13000139</v>
+        <v>22.26069718</v>
       </c>
       <c r="E3" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2378611434.820736</v>
+        <v>2393085684.676051</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.78287251</v>
+        <v>13.85227909</v>
       </c>
       <c r="E4" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2155422870.124498</v>
+        <v>2148598070.049083</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.48960557</v>
+        <v>12.43707249</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1932651373.836447</v>
+        <v>1917766035.084234</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.19875533</v>
+        <v>11.10091065</v>
       </c>
       <c r="E6" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>890638595.2895253</v>
+        <v>885537576.7106992</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.16080854</v>
+        <v>5.12589822</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>180671887.9731569</v>
+        <v>178889132.5383159</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.0469039</v>
+        <v>1.03549246</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>37522474.912046</v>
+        <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21742412</v>
+        <v>0.20974667</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17257733711.72503</v>
+        <v>17275754182.25387</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E361"/>
+  <dimension ref="A1:E369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8273,6 +8273,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="n">
+        <v>2148598070.049083</v>
+      </c>
+      <c r="D362" s="3" t="n">
+        <v>12.43707249</v>
+      </c>
+      <c r="E362" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="n">
+        <v>2393085684.676051</v>
+      </c>
+      <c r="D363" s="3" t="n">
+        <v>13.85227909</v>
+      </c>
+      <c r="E363" t="n">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="n">
+        <v>885537576.7106992</v>
+      </c>
+      <c r="D364" s="3" t="n">
+        <v>5.12589822</v>
+      </c>
+      <c r="E364" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="n">
+        <v>1917766035.084234</v>
+      </c>
+      <c r="D365" s="3" t="n">
+        <v>11.10091065</v>
+      </c>
+      <c r="E365" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="n">
+        <v>3845703323.982821</v>
+      </c>
+      <c r="D366" s="3" t="n">
+        <v>22.26069718</v>
+      </c>
+      <c r="E366" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="n">
+        <v>5869939039.959793</v>
+      </c>
+      <c r="D367" s="3" t="n">
+        <v>33.97790324</v>
+      </c>
+      <c r="E367" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="n">
+        <v>178889132.5383159</v>
+      </c>
+      <c r="D368" s="3" t="n">
+        <v>1.03549246</v>
+      </c>
+      <c r="E368" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D369" s="3" t="n">
+        <v>0.20974667</v>
+      </c>
+      <c r="E369" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5869939039.959793</v>
+        <v>5852296885.735145</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.97790324</v>
+        <v>33.88440011</v>
       </c>
       <c r="E2" t="n">
-        <v>1219</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3845703323.982821</v>
+        <v>3801675472.054118</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.26069718</v>
+        <v>22.01144188</v>
       </c>
       <c r="E3" t="n">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2393085684.676051</v>
+        <v>2408479727.608665</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.85227909</v>
+        <v>13.94493348</v>
       </c>
       <c r="E4" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2148598070.049083</v>
+        <v>2171730656.016754</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.43707249</v>
+        <v>12.57417249</v>
       </c>
       <c r="E5" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1917766035.084234</v>
+        <v>1946369689.896734</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.10091065</v>
+        <v>11.26934785</v>
       </c>
       <c r="E6" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>885537576.7106992</v>
+        <v>885538677.2799722</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12589822</v>
+        <v>5.12720859</v>
       </c>
       <c r="E7" t="n">
         <v>45</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>178889132.5383159</v>
+        <v>169034040.3681449</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.03549246</v>
+        <v>0.97869557</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20974667</v>
+        <v>0.20980003</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17275754182.25387</v>
+        <v>17271360468.21241</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E369"/>
+  <dimension ref="A1:E377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8441,6 +8441,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="n">
+        <v>2171730656.016754</v>
+      </c>
+      <c r="D370" s="3" t="n">
+        <v>12.57417249</v>
+      </c>
+      <c r="E370" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="n">
+        <v>2408479727.608665</v>
+      </c>
+      <c r="D371" s="3" t="n">
+        <v>13.94493348</v>
+      </c>
+      <c r="E371" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="n">
+        <v>885538677.2799722</v>
+      </c>
+      <c r="D372" s="3" t="n">
+        <v>5.12720859</v>
+      </c>
+      <c r="E372" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="n">
+        <v>1946369689.896734</v>
+      </c>
+      <c r="D373" s="3" t="n">
+        <v>11.26934785</v>
+      </c>
+      <c r="E373" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="n">
+        <v>3801675472.054118</v>
+      </c>
+      <c r="D374" s="3" t="n">
+        <v>22.01144188</v>
+      </c>
+      <c r="E374" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="n">
+        <v>5852296885.735145</v>
+      </c>
+      <c r="D375" s="3" t="n">
+        <v>33.88440011</v>
+      </c>
+      <c r="E375" t="n">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="n">
+        <v>169034040.3681449</v>
+      </c>
+      <c r="D376" s="3" t="n">
+        <v>0.97869557</v>
+      </c>
+      <c r="E376" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D377" s="3" t="n">
+        <v>0.20980003</v>
+      </c>
+      <c r="E377" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5852296885.735145</v>
+        <v>5835561487.834236</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.88440011</v>
+        <v>33.77020813</v>
       </c>
       <c r="E2" t="n">
-        <v>1214</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3801675472.054118</v>
+        <v>3811511151.245913</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.01144188</v>
+        <v>22.05709342</v>
       </c>
       <c r="E3" t="n">
         <v>230</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2408479727.608665</v>
+        <v>2431570386.421016</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.94493348</v>
+        <v>14.07142024</v>
       </c>
       <c r="E4" t="n">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2171730656.016754</v>
+        <v>2177449359.00349</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.57417249</v>
+        <v>12.60082996</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1946369689.896734</v>
+        <v>1936555942.138356</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.26934785</v>
+        <v>11.20678745</v>
       </c>
       <c r="E6" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>885538677.2799722</v>
+        <v>882288183.8106052</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12720859</v>
+        <v>5.10577357</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>169034040.3681449</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.97869557</v>
+        <v>0.9781946</v>
       </c>
       <c r="E8" t="n">
         <v>20</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20980003</v>
+        <v>0.20969264</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17271360468.21241</v>
+        <v>17280205870.07464</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E377"/>
+  <dimension ref="A1:E385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8609,6 +8609,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="n">
+        <v>2177449359.00349</v>
+      </c>
+      <c r="D378" s="3" t="n">
+        <v>12.60082996</v>
+      </c>
+      <c r="E378" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="n">
+        <v>2431570386.421016</v>
+      </c>
+      <c r="D379" s="3" t="n">
+        <v>14.07142024</v>
+      </c>
+      <c r="E379" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="n">
+        <v>882288183.8106052</v>
+      </c>
+      <c r="D380" s="3" t="n">
+        <v>5.10577357</v>
+      </c>
+      <c r="E380" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="n">
+        <v>1936555942.138356</v>
+      </c>
+      <c r="D381" s="3" t="n">
+        <v>11.20678745</v>
+      </c>
+      <c r="E381" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="n">
+        <v>3811511151.245913</v>
+      </c>
+      <c r="D382" s="3" t="n">
+        <v>22.05709342</v>
+      </c>
+      <c r="E382" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="n">
+        <v>5835561487.834236</v>
+      </c>
+      <c r="D383" s="3" t="n">
+        <v>33.77020813</v>
+      </c>
+      <c r="E383" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="n">
+        <v>169034040.3681449</v>
+      </c>
+      <c r="D384" s="3" t="n">
+        <v>0.9781946</v>
+      </c>
+      <c r="E384" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D385" s="3" t="n">
+        <v>0.20969264</v>
+      </c>
+      <c r="E385" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5835561487.834236</v>
+        <v>5795180014.986934</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.77020813</v>
+        <v>33.58591371</v>
       </c>
       <c r="E2" t="n">
-        <v>1211</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3811511151.245913</v>
+        <v>3851241573.011454</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.05709342</v>
+        <v>22.31983593</v>
       </c>
       <c r="E3" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2431570386.421016</v>
+        <v>2405451061.615464</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.07142024</v>
+        <v>13.94077001</v>
       </c>
       <c r="E4" t="n">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2177449359.00349</v>
+        <v>2160325061.654566</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.60082996</v>
+        <v>12.52014448</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1936555942.138356</v>
+        <v>1946364546.154181</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.20678745</v>
+        <v>11.28013824</v>
       </c>
       <c r="E6" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882288183.8106052</v>
+        <v>883148880.1066952</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.10577357</v>
+        <v>5.1182814</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>169034040.3681449</v>
+        <v>174340512.5745399</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.9781946</v>
+        <v>1.01038887</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>36235319.252875</v>
+        <v>38741729.857452</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20969264</v>
+        <v>0.22452735</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17280205870.07464</v>
+        <v>17254793379.96128</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E385"/>
+  <dimension ref="A1:E393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8777,6 +8777,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="n">
+        <v>2160325061.654566</v>
+      </c>
+      <c r="D386" s="3" t="n">
+        <v>12.52014448</v>
+      </c>
+      <c r="E386" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="n">
+        <v>2405451061.615464</v>
+      </c>
+      <c r="D387" s="3" t="n">
+        <v>13.94077001</v>
+      </c>
+      <c r="E387" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="n">
+        <v>883148880.1066952</v>
+      </c>
+      <c r="D388" s="3" t="n">
+        <v>5.1182814</v>
+      </c>
+      <c r="E388" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="n">
+        <v>1946364546.154181</v>
+      </c>
+      <c r="D389" s="3" t="n">
+        <v>11.28013824</v>
+      </c>
+      <c r="E389" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="n">
+        <v>3851241573.011454</v>
+      </c>
+      <c r="D390" s="3" t="n">
+        <v>22.31983593</v>
+      </c>
+      <c r="E390" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="n">
+        <v>5795180014.986934</v>
+      </c>
+      <c r="D391" s="3" t="n">
+        <v>33.58591371</v>
+      </c>
+      <c r="E391" t="n">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="n">
+        <v>174340512.5745399</v>
+      </c>
+      <c r="D392" s="3" t="n">
+        <v>1.01038887</v>
+      </c>
+      <c r="E392" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="n">
+        <v>38741729.857452</v>
+      </c>
+      <c r="D393" s="3" t="n">
+        <v>0.22452735</v>
+      </c>
+      <c r="E393" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5795180014.986934</v>
+        <v>5819605016.115418</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.58591371</v>
+        <v>33.73992158</v>
       </c>
       <c r="E2" t="n">
-        <v>1215</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3851241573.011454</v>
+        <v>3870801009.821117</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.31983593</v>
+        <v>22.44147535</v>
       </c>
       <c r="E3" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2405451061.615464</v>
+        <v>2362434678.39958</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.94077001</v>
+        <v>13.69652417</v>
       </c>
       <c r="E4" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2160325061.654566</v>
+        <v>2166650162.455838</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.52014448</v>
+        <v>12.56143782</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1946364546.154181</v>
+        <v>1935287916.481128</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.28013824</v>
+        <v>11.22008493</v>
       </c>
       <c r="E6" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>883148880.1066952</v>
+        <v>880009643.2604172</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.1182814</v>
+        <v>5.10197106</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>174340512.5745399</v>
+        <v>177401099.1998569</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01038887</v>
+        <v>1.02850609</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>38741729.857452</v>
+        <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.22452735</v>
+        <v>0.210079</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17254793379.96128</v>
+        <v>17248424844.98623</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E393"/>
+  <dimension ref="A1:E401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8945,6 +8945,174 @@
         <v>8</v>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="n">
+        <v>2166650162.455838</v>
+      </c>
+      <c r="D394" s="3" t="n">
+        <v>12.56143782</v>
+      </c>
+      <c r="E394" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="n">
+        <v>2362434678.39958</v>
+      </c>
+      <c r="D395" s="3" t="n">
+        <v>13.69652417</v>
+      </c>
+      <c r="E395" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="n">
+        <v>880009643.2604172</v>
+      </c>
+      <c r="D396" s="3" t="n">
+        <v>5.10197106</v>
+      </c>
+      <c r="E396" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="n">
+        <v>1935287916.481128</v>
+      </c>
+      <c r="D397" s="3" t="n">
+        <v>11.22008493</v>
+      </c>
+      <c r="E397" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="n">
+        <v>3870801009.821117</v>
+      </c>
+      <c r="D398" s="3" t="n">
+        <v>22.44147535</v>
+      </c>
+      <c r="E398" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="n">
+        <v>5819605016.115418</v>
+      </c>
+      <c r="D399" s="3" t="n">
+        <v>33.73992158</v>
+      </c>
+      <c r="E399" t="n">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="n">
+        <v>177401099.1998569</v>
+      </c>
+      <c r="D400" s="3" t="n">
+        <v>1.02850609</v>
+      </c>
+      <c r="E400" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D401" s="3" t="n">
+        <v>0.210079</v>
+      </c>
+      <c r="E401" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5819605016.115418</v>
+        <v>5823368059.011282</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.73992158</v>
+        <v>33.73747767</v>
       </c>
       <c r="E2" t="n">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3870801009.821117</v>
+        <v>3799882465.806445</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.44147535</v>
+        <v>22.01448518</v>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2362434678.39958</v>
+        <v>2423592769.425795</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.69652417</v>
+        <v>14.04099932</v>
       </c>
       <c r="E4" t="n">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2166650162.455838</v>
+        <v>2181579652.53268</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.56143782</v>
+        <v>12.63890485</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1935287916.481128</v>
+        <v>1940712577.322234</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.22008493</v>
+        <v>11.24344994</v>
       </c>
       <c r="E6" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>880009643.2604172</v>
+        <v>882283312.6163192</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.10197106</v>
+        <v>5.11147729</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>177401099.1998569</v>
+        <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02850609</v>
+        <v>1.00327772</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.210079</v>
+        <v>0.20992805</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17248424844.98623</v>
+        <v>17260828199.18048</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E401"/>
+  <dimension ref="A1:E409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9113,6 +9113,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="n">
+        <v>2181579652.53268</v>
+      </c>
+      <c r="D402" s="3" t="n">
+        <v>12.63890485</v>
+      </c>
+      <c r="E402" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="n">
+        <v>2423592769.425795</v>
+      </c>
+      <c r="D403" s="3" t="n">
+        <v>14.04099932</v>
+      </c>
+      <c r="E403" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="n">
+        <v>882283312.6163192</v>
+      </c>
+      <c r="D404" s="3" t="n">
+        <v>5.11147729</v>
+      </c>
+      <c r="E404" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="n">
+        <v>1940712577.322234</v>
+      </c>
+      <c r="D405" s="3" t="n">
+        <v>11.24344994</v>
+      </c>
+      <c r="E405" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="n">
+        <v>3799882465.806445</v>
+      </c>
+      <c r="D406" s="3" t="n">
+        <v>22.01448518</v>
+      </c>
+      <c r="E406" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="n">
+        <v>5823368059.011282</v>
+      </c>
+      <c r="D407" s="3" t="n">
+        <v>33.73747767</v>
+      </c>
+      <c r="E407" t="n">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D408" s="3" t="n">
+        <v>1.00327772</v>
+      </c>
+      <c r="E408" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D409" s="3" t="n">
+        <v>0.20992805</v>
+      </c>
+      <c r="E409" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5823368059.011282</v>
+        <v>5829472834.087463</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.73747767</v>
+        <v>33.71856051</v>
       </c>
       <c r="E2" t="n">
         <v>1217</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3799882465.806445</v>
+        <v>3813500439.481496</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.01448518</v>
+        <v>22.05786852</v>
       </c>
       <c r="E3" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2423592769.425795</v>
+        <v>2451887804.258129</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.04099932</v>
+        <v>14.18209324</v>
       </c>
       <c r="E4" t="n">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2181579652.53268</v>
+        <v>2189901482.372076</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.63890485</v>
+        <v>12.66672438</v>
       </c>
       <c r="E5" t="n">
         <v>49</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1940712577.322234</v>
+        <v>1912161911.524138</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.24344994</v>
+        <v>11.06023631</v>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -596,7 +596,7 @@
         <v>882283312.6163192</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.11147729</v>
+        <v>5.10326133</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00327772</v>
+        <v>1.00166509</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20992805</v>
+        <v>0.20959062</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17260828199.18048</v>
+        <v>17288617146.80535</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E409"/>
+  <dimension ref="A1:E417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9281,6 +9281,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="n">
+        <v>2189901482.372076</v>
+      </c>
+      <c r="D410" s="3" t="n">
+        <v>12.66672438</v>
+      </c>
+      <c r="E410" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="n">
+        <v>2451887804.258129</v>
+      </c>
+      <c r="D411" s="3" t="n">
+        <v>14.18209324</v>
+      </c>
+      <c r="E411" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="n">
+        <v>882283312.6163192</v>
+      </c>
+      <c r="D412" s="3" t="n">
+        <v>5.10326133</v>
+      </c>
+      <c r="E412" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="n">
+        <v>1912161911.524138</v>
+      </c>
+      <c r="D413" s="3" t="n">
+        <v>11.06023631</v>
+      </c>
+      <c r="E413" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="n">
+        <v>3813500439.481496</v>
+      </c>
+      <c r="D414" s="3" t="n">
+        <v>22.05786852</v>
+      </c>
+      <c r="E414" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="n">
+        <v>5829472834.087463</v>
+      </c>
+      <c r="D415" s="3" t="n">
+        <v>33.71856051</v>
+      </c>
+      <c r="E415" t="n">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D416" s="3" t="n">
+        <v>1.00166509</v>
+      </c>
+      <c r="E416" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D417" s="3" t="n">
+        <v>0.20959062</v>
+      </c>
+      <c r="E417" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5829472834.087463</v>
+        <v>5826456950.905224</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.71856051</v>
+        <v>33.75521404</v>
       </c>
       <c r="E2" t="n">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3813500439.481496</v>
+        <v>3802187017.964299</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.05786852</v>
+        <v>22.02773275</v>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2451887804.258129</v>
+        <v>2437188413.570158</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.18209324</v>
+        <v>14.11969869</v>
       </c>
       <c r="E4" t="n">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2189901482.372076</v>
+        <v>2211738732.206295</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.66672438</v>
+        <v>12.81357005</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1912161911.524138</v>
+        <v>1886222526.787779</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.06023631</v>
+        <v>10.92771227</v>
       </c>
       <c r="E6" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882283312.6163192</v>
+        <v>885349316.7320863</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.10326133</v>
+        <v>5.12921591</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>173174043.2128489</v>
+        <v>175531234.0931889</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00166509</v>
+        <v>1.01692923</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20959062</v>
+        <v>0.20992706</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17288617146.80535</v>
+        <v>17260909511.51191</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E417"/>
+  <dimension ref="A1:E425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9449,6 +9449,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="n">
+        <v>2211738732.206295</v>
+      </c>
+      <c r="D418" s="3" t="n">
+        <v>12.81357005</v>
+      </c>
+      <c r="E418" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="n">
+        <v>2437188413.570158</v>
+      </c>
+      <c r="D419" s="3" t="n">
+        <v>14.11969869</v>
+      </c>
+      <c r="E419" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="n">
+        <v>885349316.7320863</v>
+      </c>
+      <c r="D420" s="3" t="n">
+        <v>5.12921591</v>
+      </c>
+      <c r="E420" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="n">
+        <v>1886222526.787779</v>
+      </c>
+      <c r="D421" s="3" t="n">
+        <v>10.92771227</v>
+      </c>
+      <c r="E421" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="n">
+        <v>3802187017.964299</v>
+      </c>
+      <c r="D422" s="3" t="n">
+        <v>22.02773275</v>
+      </c>
+      <c r="E422" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="n">
+        <v>5826456950.905224</v>
+      </c>
+      <c r="D423" s="3" t="n">
+        <v>33.75521404</v>
+      </c>
+      <c r="E423" t="n">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="n">
+        <v>175531234.0931889</v>
+      </c>
+      <c r="D424" s="3" t="n">
+        <v>1.01692923</v>
+      </c>
+      <c r="E424" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D425" s="3" t="n">
+        <v>0.20992706</v>
+      </c>
+      <c r="E425" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5826456950.905224</v>
+        <v>5849892850.335894</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.75521404</v>
+        <v>33.90662328</v>
       </c>
       <c r="E2" t="n">
-        <v>1218</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3802187017.964299</v>
+        <v>3771814010.298801</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.02773275</v>
+        <v>21.86184944</v>
       </c>
       <c r="E3" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2437188413.570158</v>
+        <v>2421921589.07901</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.11969869</v>
+        <v>14.03772429</v>
       </c>
       <c r="E4" t="n">
         <v>302</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2211738732.206295</v>
+        <v>2199131768.132521</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.81357005</v>
+        <v>12.74640995</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1886222526.787779</v>
+        <v>1914384773.996582</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.92771227</v>
+        <v>11.09598501</v>
       </c>
       <c r="E6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>885349316.7320863</v>
+        <v>886395906.6334802</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12921591</v>
+        <v>5.1376483</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175531234.0931889</v>
+        <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01692923</v>
+        <v>1.00373583</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20992706</v>
+        <v>0.2100239</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17260909511.51191</v>
+        <v>17252950260.94201</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E425"/>
+  <dimension ref="A1:E433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9617,6 +9617,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="n">
+        <v>2199131768.132521</v>
+      </c>
+      <c r="D426" s="3" t="n">
+        <v>12.74640995</v>
+      </c>
+      <c r="E426" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="n">
+        <v>2421921589.07901</v>
+      </c>
+      <c r="D427" s="3" t="n">
+        <v>14.03772429</v>
+      </c>
+      <c r="E427" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="n">
+        <v>886395906.6334802</v>
+      </c>
+      <c r="D428" s="3" t="n">
+        <v>5.1376483</v>
+      </c>
+      <c r="E428" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="n">
+        <v>1914384773.996582</v>
+      </c>
+      <c r="D429" s="3" t="n">
+        <v>11.09598501</v>
+      </c>
+      <c r="E429" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="n">
+        <v>3771814010.298801</v>
+      </c>
+      <c r="D430" s="3" t="n">
+        <v>21.86184944</v>
+      </c>
+      <c r="E430" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="n">
+        <v>5849892850.335894</v>
+      </c>
+      <c r="D431" s="3" t="n">
+        <v>33.90662328</v>
+      </c>
+      <c r="E431" t="n">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D432" s="3" t="n">
+        <v>1.00373583</v>
+      </c>
+      <c r="E432" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D433" s="3" t="n">
+        <v>0.2100239</v>
+      </c>
+      <c r="E433" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5849892850.335894</v>
+        <v>5817783120.632646</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.90662328</v>
+        <v>33.71563342</v>
       </c>
       <c r="E2" t="n">
-        <v>1220</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3771814010.298801</v>
+        <v>3769734343.47882</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.86184944</v>
+        <v>21.84663446</v>
       </c>
       <c r="E3" t="n">
         <v>226</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2421921589.07901</v>
+        <v>2448370804.314725</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.03772429</v>
+        <v>14.18897384</v>
       </c>
       <c r="E4" t="n">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2199131768.132521</v>
+        <v>2195010013.649335</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.74640995</v>
+        <v>12.72067924</v>
       </c>
       <c r="E5" t="n">
         <v>49</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1914384773.996582</v>
+        <v>1928742122.37768</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.09598501</v>
+        <v>11.17758449</v>
       </c>
       <c r="E6" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>886395906.6334802</v>
+        <v>886396834.4034802</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.1376483</v>
+        <v>5.13691042</v>
       </c>
       <c r="E7" t="n">
         <v>45</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00373583</v>
+        <v>1.00359062</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.2100239</v>
+        <v>0.20999352</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17252950260.94201</v>
+        <v>17255446601.32241</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E433"/>
+  <dimension ref="A1:E441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9785,6 +9785,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="n">
+        <v>2195010013.649335</v>
+      </c>
+      <c r="D434" s="3" t="n">
+        <v>12.72067924</v>
+      </c>
+      <c r="E434" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="n">
+        <v>2448370804.314725</v>
+      </c>
+      <c r="D435" s="3" t="n">
+        <v>14.18897384</v>
+      </c>
+      <c r="E435" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="n">
+        <v>886396834.4034802</v>
+      </c>
+      <c r="D436" s="3" t="n">
+        <v>5.13691042</v>
+      </c>
+      <c r="E436" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="n">
+        <v>1928742122.37768</v>
+      </c>
+      <c r="D437" s="3" t="n">
+        <v>11.17758449</v>
+      </c>
+      <c r="E437" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="n">
+        <v>3769734343.47882</v>
+      </c>
+      <c r="D438" s="3" t="n">
+        <v>21.84663446</v>
+      </c>
+      <c r="E438" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="n">
+        <v>5817783120.632646</v>
+      </c>
+      <c r="D439" s="3" t="n">
+        <v>33.71563342</v>
+      </c>
+      <c r="E439" t="n">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D440" s="3" t="n">
+        <v>1.00359062</v>
+      </c>
+      <c r="E440" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D441" s="3" t="n">
+        <v>0.20999352</v>
+      </c>
+      <c r="E441" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5817783120.632646</v>
+        <v>5834950359.623088</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.71563342</v>
+        <v>33.90504505</v>
       </c>
       <c r="E2" t="n">
-        <v>1214</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3769734343.47882</v>
+        <v>3775029139.883642</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.84663446</v>
+        <v>21.93549647</v>
       </c>
       <c r="E3" t="n">
         <v>226</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2448370804.314725</v>
+        <v>2417743684.423326</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.18897384</v>
+        <v>14.04874137</v>
       </c>
       <c r="E4" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2195010013.649335</v>
+        <v>2186567919.667929</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.72067924</v>
+        <v>12.70545236</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1928742122.37768</v>
+        <v>1903714472.533341</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.17758449</v>
+        <v>11.06188073</v>
       </c>
       <c r="E6" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>886396834.4034802</v>
+        <v>882266840.1720252</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.13691042</v>
+        <v>5.12657266</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00359062</v>
+        <v>1.00625942</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20999352</v>
+        <v>0.21055194</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17255446601.32241</v>
+        <v>17209681778.76907</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E441"/>
+  <dimension ref="A1:E449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9953,6 +9953,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="n">
+        <v>2186567919.667929</v>
+      </c>
+      <c r="D442" s="3" t="n">
+        <v>12.70545236</v>
+      </c>
+      <c r="E442" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="n">
+        <v>2417743684.423326</v>
+      </c>
+      <c r="D443" s="3" t="n">
+        <v>14.04874137</v>
+      </c>
+      <c r="E443" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="n">
+        <v>882266840.1720252</v>
+      </c>
+      <c r="D444" s="3" t="n">
+        <v>5.12657266</v>
+      </c>
+      <c r="E444" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="n">
+        <v>1903714472.533341</v>
+      </c>
+      <c r="D445" s="3" t="n">
+        <v>11.06188073</v>
+      </c>
+      <c r="E445" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="n">
+        <v>3775029139.883642</v>
+      </c>
+      <c r="D446" s="3" t="n">
+        <v>21.93549647</v>
+      </c>
+      <c r="E446" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="n">
+        <v>5834950359.623088</v>
+      </c>
+      <c r="D447" s="3" t="n">
+        <v>33.90504505</v>
+      </c>
+      <c r="E447" t="n">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D448" s="3" t="n">
+        <v>1.00625942</v>
+      </c>
+      <c r="E448" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D449" s="3" t="n">
+        <v>0.21055194</v>
+      </c>
+      <c r="E449" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5834950359.623088</v>
+        <v>5841624550.363265</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.90504505</v>
+        <v>33.92386642</v>
       </c>
       <c r="E2" t="n">
         <v>1224</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3775029139.883642</v>
+        <v>3779006693.347796</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.93549647</v>
+        <v>21.9456963</v>
       </c>
       <c r="E3" t="n">
         <v>226</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2417743684.423326</v>
+        <v>2423087320.757</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.04874137</v>
+        <v>14.07151211</v>
       </c>
       <c r="E4" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2186567919.667929</v>
+        <v>2188562462.72749</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.70545236</v>
+        <v>12.70956392</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1903714472.533341</v>
+        <v>1895850568.713861</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.06188073</v>
+        <v>11.00970815</v>
       </c>
       <c r="E6" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882266840.1720252</v>
+        <v>882266708.3092612</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12657266</v>
+        <v>5.12355727</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00625942</v>
+        <v>1.0056677</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21055194</v>
+        <v>0.21042813</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17209681778.76907</v>
+        <v>17219807666.6844</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E449"/>
+  <dimension ref="A1:E457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10121,6 +10121,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="n">
+        <v>2188562462.72749</v>
+      </c>
+      <c r="D450" s="3" t="n">
+        <v>12.70956392</v>
+      </c>
+      <c r="E450" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="n">
+        <v>2423087320.757</v>
+      </c>
+      <c r="D451" s="3" t="n">
+        <v>14.07151211</v>
+      </c>
+      <c r="E451" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="n">
+        <v>882266708.3092612</v>
+      </c>
+      <c r="D452" s="3" t="n">
+        <v>5.12355727</v>
+      </c>
+      <c r="E452" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="n">
+        <v>1895850568.713861</v>
+      </c>
+      <c r="D453" s="3" t="n">
+        <v>11.00970815</v>
+      </c>
+      <c r="E453" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="n">
+        <v>3779006693.347796</v>
+      </c>
+      <c r="D454" s="3" t="n">
+        <v>21.9456963</v>
+      </c>
+      <c r="E454" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="n">
+        <v>5841624550.363265</v>
+      </c>
+      <c r="D455" s="3" t="n">
+        <v>33.92386642</v>
+      </c>
+      <c r="E455" t="n">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D456" s="3" t="n">
+        <v>1.0056677</v>
+      </c>
+      <c r="E456" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D457" s="3" t="n">
+        <v>0.21042813</v>
+      </c>
+      <c r="E457" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5841624550.363265</v>
+        <v>5840836154.886524</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.92386642</v>
+        <v>33.89940536</v>
       </c>
       <c r="E2" t="n">
         <v>1224</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3779006693.347796</v>
+        <v>3783803161.962616</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.9456963</v>
+        <v>21.96067032</v>
       </c>
       <c r="E3" t="n">
         <v>226</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2423087320.757</v>
+        <v>2424046991.895899</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.07151211</v>
+        <v>14.06883354</v>
       </c>
       <c r="E4" t="n">
         <v>303</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2188562462.72749</v>
+        <v>2194036061.705335</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.70956392</v>
+        <v>12.73388191</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1895850568.713861</v>
+        <v>1895504210.298803</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.00970815</v>
+        <v>11.00124432</v>
       </c>
       <c r="E6" t="n">
         <v>127</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882266708.3092612</v>
+        <v>882271464.0092661</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12355727</v>
+        <v>5.12058157</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.0056677</v>
+        <v>1.0050782</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21042813</v>
+        <v>0.21030478</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17219807666.6844</v>
+        <v>17229907407.22417</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E457"/>
+  <dimension ref="A1:E465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10289,6 +10289,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="n">
+        <v>2194036061.705335</v>
+      </c>
+      <c r="D458" s="3" t="n">
+        <v>12.73388191</v>
+      </c>
+      <c r="E458" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="n">
+        <v>2424046991.895899</v>
+      </c>
+      <c r="D459" s="3" t="n">
+        <v>14.06883354</v>
+      </c>
+      <c r="E459" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="n">
+        <v>882271464.0092661</v>
+      </c>
+      <c r="D460" s="3" t="n">
+        <v>5.12058157</v>
+      </c>
+      <c r="E460" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="n">
+        <v>1895504210.298803</v>
+      </c>
+      <c r="D461" s="3" t="n">
+        <v>11.00124432</v>
+      </c>
+      <c r="E461" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="n">
+        <v>3783803161.962616</v>
+      </c>
+      <c r="D462" s="3" t="n">
+        <v>21.96067032</v>
+      </c>
+      <c r="E462" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="n">
+        <v>5840836154.886524</v>
+      </c>
+      <c r="D463" s="3" t="n">
+        <v>33.89940536</v>
+      </c>
+      <c r="E463" t="n">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D464" s="3" t="n">
+        <v>1.0050782</v>
+      </c>
+      <c r="E464" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D465" s="3" t="n">
+        <v>0.21030478</v>
+      </c>
+      <c r="E465" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5840836154.886524</v>
+        <v>5848843271.224671</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.89940536</v>
+        <v>33.92137012</v>
       </c>
       <c r="E2" t="n">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3783803161.962616</v>
+        <v>3782330198.23419</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.96067032</v>
+        <v>21.93627297</v>
       </c>
       <c r="E3" t="n">
         <v>226</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2424046991.895899</v>
+        <v>2429285730.028086</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.06883354</v>
+        <v>14.08905942</v>
       </c>
       <c r="E4" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2194036061.705335</v>
+        <v>2199522848.947846</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.73388191</v>
+        <v>12.75651017</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1895504210.298803</v>
+        <v>1890692711.434958</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.00124432</v>
+        <v>10.96539679</v>
       </c>
       <c r="E6" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882271464.0092661</v>
+        <v>882271509.7852962</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12058157</v>
+        <v>5.116885</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.0050782</v>
+        <v>1.00435258</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21030478</v>
+        <v>0.21015295</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17229907407.22417</v>
+        <v>17242355632.12077</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E465"/>
+  <dimension ref="A1:E473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10457,6 +10457,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="n">
+        <v>2199522848.947846</v>
+      </c>
+      <c r="D466" s="3" t="n">
+        <v>12.75651017</v>
+      </c>
+      <c r="E466" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="n">
+        <v>2429285730.028086</v>
+      </c>
+      <c r="D467" s="3" t="n">
+        <v>14.08905942</v>
+      </c>
+      <c r="E467" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="n">
+        <v>882271509.7852962</v>
+      </c>
+      <c r="D468" s="3" t="n">
+        <v>5.116885</v>
+      </c>
+      <c r="E468" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="n">
+        <v>1890692711.434958</v>
+      </c>
+      <c r="D469" s="3" t="n">
+        <v>10.96539679</v>
+      </c>
+      <c r="E469" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="n">
+        <v>3782330198.23419</v>
+      </c>
+      <c r="D470" s="3" t="n">
+        <v>21.93627297</v>
+      </c>
+      <c r="E470" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="n">
+        <v>5848843271.224671</v>
+      </c>
+      <c r="D471" s="3" t="n">
+        <v>33.92137012</v>
+      </c>
+      <c r="E471" t="n">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D472" s="3" t="n">
+        <v>1.00435258</v>
+      </c>
+      <c r="E472" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D473" s="3" t="n">
+        <v>0.21015295</v>
+      </c>
+      <c r="E473" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5848843271.224671</v>
+        <v>5849366708.821562</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.92137012</v>
+        <v>33.94517669</v>
       </c>
       <c r="E2" t="n">
         <v>1225</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3782330198.23419</v>
+        <v>3770987799.897578</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.93627297</v>
+        <v>21.88388138</v>
       </c>
       <c r="E3" t="n">
         <v>226</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2429285730.028086</v>
+        <v>2425923363.219282</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.08905942</v>
+        <v>14.07817313</v>
       </c>
       <c r="E4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2199522848.947846</v>
+        <v>2200958750.192526</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.75651017</v>
+        <v>12.77265342</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1890692711.434958</v>
+        <v>1892887664.286747</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.96539679</v>
+        <v>10.98484835</v>
       </c>
       <c r="E6" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -596,7 +596,7 @@
         <v>882271509.7852962</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.116885</v>
+        <v>5.12001791</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00435258</v>
+        <v>1.00496751</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21015295</v>
+        <v>0.21028162</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17242355632.12077</v>
+        <v>17231805158.66872</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E473"/>
+  <dimension ref="A1:E481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10625,6 +10625,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="n">
+        <v>2200958750.192526</v>
+      </c>
+      <c r="D474" s="3" t="n">
+        <v>12.77265342</v>
+      </c>
+      <c r="E474" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="n">
+        <v>2425923363.219282</v>
+      </c>
+      <c r="D475" s="3" t="n">
+        <v>14.07817313</v>
+      </c>
+      <c r="E475" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="n">
+        <v>882271509.7852962</v>
+      </c>
+      <c r="D476" s="3" t="n">
+        <v>5.12001791</v>
+      </c>
+      <c r="E476" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="n">
+        <v>1892887664.286747</v>
+      </c>
+      <c r="D477" s="3" t="n">
+        <v>10.98484835</v>
+      </c>
+      <c r="E477" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="n">
+        <v>3770987799.897578</v>
+      </c>
+      <c r="D478" s="3" t="n">
+        <v>21.88388138</v>
+      </c>
+      <c r="E478" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="n">
+        <v>5849366708.821562</v>
+      </c>
+      <c r="D479" s="3" t="n">
+        <v>33.94517669</v>
+      </c>
+      <c r="E479" t="n">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D480" s="3" t="n">
+        <v>1.00496751</v>
+      </c>
+      <c r="E480" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D481" s="3" t="n">
+        <v>0.21028162</v>
+      </c>
+      <c r="E481" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5849366708.821562</v>
+        <v>5863822085.411501</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.94517669</v>
+        <v>34.00295779</v>
       </c>
       <c r="E2" t="n">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3770987799.897578</v>
+        <v>3769952843.484816</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.88388138</v>
+        <v>21.86109086</v>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2425923363.219282</v>
+        <v>2426211643.951117</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.07817313</v>
+        <v>14.0690442</v>
       </c>
       <c r="E4" t="n">
         <v>303</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2200958750.192526</v>
+        <v>2201098476.845304</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.77265342</v>
+        <v>12.76366464</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1892887664.286747</v>
+        <v>1892269336.872321</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.98484835</v>
+        <v>10.97283537</v>
       </c>
       <c r="E6" t="n">
         <v>127</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882271509.7852962</v>
+        <v>882271583.5852962</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12001791</v>
+        <v>5.11609032</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00496751</v>
+        <v>1.00419651</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21028162</v>
+        <v>0.2101203</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17231805158.66872</v>
+        <v>17245035332.61608</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E481"/>
+  <dimension ref="A1:E489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10793,6 +10793,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="n">
+        <v>2201098476.845304</v>
+      </c>
+      <c r="D482" s="3" t="n">
+        <v>12.76366464</v>
+      </c>
+      <c r="E482" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="n">
+        <v>2426211643.951117</v>
+      </c>
+      <c r="D483" s="3" t="n">
+        <v>14.0690442</v>
+      </c>
+      <c r="E483" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="n">
+        <v>882271583.5852962</v>
+      </c>
+      <c r="D484" s="3" t="n">
+        <v>5.11609032</v>
+      </c>
+      <c r="E484" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="n">
+        <v>1892269336.872321</v>
+      </c>
+      <c r="D485" s="3" t="n">
+        <v>10.97283537</v>
+      </c>
+      <c r="E485" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="n">
+        <v>3769952843.484816</v>
+      </c>
+      <c r="D486" s="3" t="n">
+        <v>21.86109086</v>
+      </c>
+      <c r="E486" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="n">
+        <v>5863822085.411501</v>
+      </c>
+      <c r="D487" s="3" t="n">
+        <v>34.00295779</v>
+      </c>
+      <c r="E487" t="n">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D488" s="3" t="n">
+        <v>1.00419651</v>
+      </c>
+      <c r="E488" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D489" s="3" t="n">
+        <v>0.2101203</v>
+      </c>
+      <c r="E489" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5863822085.411501</v>
+        <v>5832833681.782937</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.00295779</v>
+        <v>33.87822816</v>
       </c>
       <c r="E2" t="n">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3769952843.484816</v>
+        <v>3771306902.605789</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.86109086</v>
+        <v>21.9044812</v>
       </c>
       <c r="E3" t="n">
         <v>225</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2426211643.951117</v>
+        <v>2426041079.411089</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.0690442</v>
+        <v>14.09091664</v>
       </c>
       <c r="E4" t="n">
         <v>303</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2201098476.845304</v>
+        <v>2200668872.911122</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.76366464</v>
+        <v>12.7819112</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1892269336.872321</v>
+        <v>1894525545.125091</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.97283537</v>
+        <v>11.00377144</v>
       </c>
       <c r="E6" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882271583.5852962</v>
+        <v>882271051.2116982</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.11609032</v>
+        <v>5.12440121</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00419651</v>
+        <v>1.0058284</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.2101203</v>
+        <v>0.21046175</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17245035332.61608</v>
+        <v>17217056495.51345</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E489"/>
+  <dimension ref="A1:E497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10961,6 +10961,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="n">
+        <v>2200668872.911122</v>
+      </c>
+      <c r="D490" s="3" t="n">
+        <v>12.7819112</v>
+      </c>
+      <c r="E490" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="n">
+        <v>2426041079.411089</v>
+      </c>
+      <c r="D491" s="3" t="n">
+        <v>14.09091664</v>
+      </c>
+      <c r="E491" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="n">
+        <v>882271051.2116982</v>
+      </c>
+      <c r="D492" s="3" t="n">
+        <v>5.12440121</v>
+      </c>
+      <c r="E492" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="n">
+        <v>1894525545.125091</v>
+      </c>
+      <c r="D493" s="3" t="n">
+        <v>11.00377144</v>
+      </c>
+      <c r="E493" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="n">
+        <v>3771306902.605789</v>
+      </c>
+      <c r="D494" s="3" t="n">
+        <v>21.9044812</v>
+      </c>
+      <c r="E494" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C495" s="2" t="n">
+        <v>5832833681.782937</v>
+      </c>
+      <c r="D495" s="3" t="n">
+        <v>33.87822816</v>
+      </c>
+      <c r="E495" t="n">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D496" s="3" t="n">
+        <v>1.0058284</v>
+      </c>
+      <c r="E496" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C497" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D497" s="3" t="n">
+        <v>0.21046175</v>
+      </c>
+      <c r="E497" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5832833681.782937</v>
+        <v>5857830712.754494</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.87822816</v>
+        <v>33.99488485</v>
       </c>
       <c r="E2" t="n">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3771306902.605789</v>
+        <v>3763863620.484129</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.9044812</v>
+        <v>21.84291705</v>
       </c>
       <c r="E3" t="n">
         <v>225</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2426041079.411089</v>
+        <v>2427040995.743268</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.09091664</v>
+        <v>14.08490331</v>
       </c>
       <c r="E4" t="n">
         <v>303</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2200668872.911122</v>
+        <v>2198860060.596896</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.7819112</v>
+        <v>12.76069559</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1894525545.125091</v>
+        <v>1892230106.786072</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.00377144</v>
+        <v>10.98122287</v>
       </c>
       <c r="E6" t="n">
         <v>128</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882271051.2116982</v>
+        <v>882271406.1644422</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12440121</v>
+        <v>5.12010612</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.0058284</v>
+        <v>1.00498494</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21046175</v>
+        <v>0.21028527</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17217056495.51345</v>
+        <v>17231506264.99503</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E497"/>
+  <dimension ref="A1:E505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11129,6 +11129,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="n">
+        <v>2198860060.596896</v>
+      </c>
+      <c r="D498" s="3" t="n">
+        <v>12.76069559</v>
+      </c>
+      <c r="E498" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C499" s="2" t="n">
+        <v>2427040995.743268</v>
+      </c>
+      <c r="D499" s="3" t="n">
+        <v>14.08490331</v>
+      </c>
+      <c r="E499" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C500" s="2" t="n">
+        <v>882271406.1644422</v>
+      </c>
+      <c r="D500" s="3" t="n">
+        <v>5.12010612</v>
+      </c>
+      <c r="E500" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C501" s="2" t="n">
+        <v>1892230106.786072</v>
+      </c>
+      <c r="D501" s="3" t="n">
+        <v>10.98122287</v>
+      </c>
+      <c r="E501" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C502" s="2" t="n">
+        <v>3763863620.484129</v>
+      </c>
+      <c r="D502" s="3" t="n">
+        <v>21.84291705</v>
+      </c>
+      <c r="E502" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C503" s="2" t="n">
+        <v>5857830712.754494</v>
+      </c>
+      <c r="D503" s="3" t="n">
+        <v>33.99488485</v>
+      </c>
+      <c r="E503" t="n">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D504" s="3" t="n">
+        <v>1.00498494</v>
+      </c>
+      <c r="E504" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C505" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D505" s="3" t="n">
+        <v>0.21028527</v>
+      </c>
+      <c r="E505" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5857830712.754494</v>
+        <v>5861338320.76904</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.99488485</v>
+        <v>33.97932509</v>
       </c>
       <c r="E2" t="n">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3763863620.484129</v>
+        <v>3771406445.578047</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.84291705</v>
+        <v>21.86358109</v>
       </c>
       <c r="E3" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2427040995.743268</v>
+        <v>2430692560.945939</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.08490331</v>
+        <v>14.09120037</v>
       </c>
       <c r="E4" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2198860060.596896</v>
+        <v>2202579757.741621</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.76069559</v>
+        <v>12.76878582</v>
       </c>
       <c r="E5" t="n">
         <v>46</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1892230106.786072</v>
+        <v>1892021226.312317</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.98122287</v>
+        <v>10.96841725</v>
       </c>
       <c r="E6" t="n">
         <v>128</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882271406.1644422</v>
+        <v>882271986.0144521</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12010612</v>
+        <v>5.11470333</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00498494</v>
+        <v>1.00392381</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21028527</v>
+        <v>0.21006324</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17231506264.99503</v>
+        <v>17249719659.82714</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E505"/>
+  <dimension ref="A1:E513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11297,6 +11297,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="n">
+        <v>2202579757.741621</v>
+      </c>
+      <c r="D506" s="3" t="n">
+        <v>12.76878582</v>
+      </c>
+      <c r="E506" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C507" s="2" t="n">
+        <v>2430692560.945939</v>
+      </c>
+      <c r="D507" s="3" t="n">
+        <v>14.09120037</v>
+      </c>
+      <c r="E507" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="n">
+        <v>882271986.0144521</v>
+      </c>
+      <c r="D508" s="3" t="n">
+        <v>5.11470333</v>
+      </c>
+      <c r="E508" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C509" s="2" t="n">
+        <v>1892021226.312317</v>
+      </c>
+      <c r="D509" s="3" t="n">
+        <v>10.96841725</v>
+      </c>
+      <c r="E509" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C510" s="2" t="n">
+        <v>3771406445.578047</v>
+      </c>
+      <c r="D510" s="3" t="n">
+        <v>21.86358109</v>
+      </c>
+      <c r="E510" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C511" s="2" t="n">
+        <v>5861338320.76904</v>
+      </c>
+      <c r="D511" s="3" t="n">
+        <v>33.97932509</v>
+      </c>
+      <c r="E511" t="n">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C512" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D512" s="3" t="n">
+        <v>1.00392381</v>
+      </c>
+      <c r="E512" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C513" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D513" s="3" t="n">
+        <v>0.21006324</v>
+      </c>
+      <c r="E513" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5861338320.76904</v>
+        <v>5835251226.568334</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.97932509</v>
+        <v>33.86773096</v>
       </c>
       <c r="E2" t="n">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3771406445.578047</v>
+        <v>3769704990.711752</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.86358109</v>
+        <v>21.87932438</v>
       </c>
       <c r="E3" t="n">
         <v>226</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2430692560.945939</v>
+        <v>2433086583.142142</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.09120037</v>
+        <v>14.12160652</v>
       </c>
       <c r="E4" t="n">
         <v>304</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2202579757.741621</v>
+        <v>2210533428.443464</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.76878582</v>
+        <v>12.82991058</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1892021226.312317</v>
+        <v>1889273502.016448</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.96841725</v>
+        <v>10.96532166</v>
       </c>
       <c r="E6" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882271986.0144521</v>
+        <v>882271972.7577871</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.11470333</v>
+        <v>5.12069638</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00392381</v>
+        <v>1.00510015</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21006324</v>
+        <v>0.21030938</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17249719659.82714</v>
+        <v>17229531066.10565</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E513"/>
+  <dimension ref="A1:E521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11465,6 +11465,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="n">
+        <v>2210533428.443464</v>
+      </c>
+      <c r="D514" s="3" t="n">
+        <v>12.82991058</v>
+      </c>
+      <c r="E514" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C515" s="2" t="n">
+        <v>2433086583.142142</v>
+      </c>
+      <c r="D515" s="3" t="n">
+        <v>14.12160652</v>
+      </c>
+      <c r="E515" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C516" s="2" t="n">
+        <v>882271972.7577871</v>
+      </c>
+      <c r="D516" s="3" t="n">
+        <v>5.12069638</v>
+      </c>
+      <c r="E516" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C517" s="2" t="n">
+        <v>1889273502.016448</v>
+      </c>
+      <c r="D517" s="3" t="n">
+        <v>10.96532166</v>
+      </c>
+      <c r="E517" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C518" s="2" t="n">
+        <v>3769704990.711752</v>
+      </c>
+      <c r="D518" s="3" t="n">
+        <v>21.87932438</v>
+      </c>
+      <c r="E518" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C519" s="2" t="n">
+        <v>5835251226.568334</v>
+      </c>
+      <c r="D519" s="3" t="n">
+        <v>33.86773096</v>
+      </c>
+      <c r="E519" t="n">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C520" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D520" s="3" t="n">
+        <v>1.00510015</v>
+      </c>
+      <c r="E520" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C521" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D521" s="3" t="n">
+        <v>0.21030938</v>
+      </c>
+      <c r="E521" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5835251226.568334</v>
+        <v>5837931203.545683</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.86773096</v>
+        <v>33.84173386</v>
       </c>
       <c r="E2" t="n">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3769704990.711752</v>
+        <v>3772820396.145967</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.87932438</v>
+        <v>21.87055299</v>
       </c>
       <c r="E3" t="n">
         <v>226</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2433086583.142142</v>
+        <v>2431361877.452255</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.12160652</v>
+        <v>14.09429106</v>
       </c>
       <c r="E4" t="n">
         <v>304</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2210533428.443464</v>
+        <v>2223486898.746715</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.82991058</v>
+        <v>12.88926663</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1889273502.016448</v>
+        <v>1890887686.185818</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.96532166</v>
+        <v>10.96123192</v>
       </c>
       <c r="E6" t="n">
         <v>127</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882271972.7577871</v>
+        <v>882271631.4190582</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12069638</v>
+        <v>5.1144148</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>173174043.2128489</v>
+        <v>175690866.6797449</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00510015</v>
+        <v>1.01845728</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21030938</v>
+        <v>0.21005147</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17229531066.10565</v>
+        <v>17250685879.42812</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E521"/>
+  <dimension ref="A1:E529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11633,6 +11633,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C522" s="2" t="n">
+        <v>2223486898.746715</v>
+      </c>
+      <c r="D522" s="3" t="n">
+        <v>12.88926663</v>
+      </c>
+      <c r="E522" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C523" s="2" t="n">
+        <v>2431361877.452255</v>
+      </c>
+      <c r="D523" s="3" t="n">
+        <v>14.09429106</v>
+      </c>
+      <c r="E523" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C524" s="2" t="n">
+        <v>882271631.4190582</v>
+      </c>
+      <c r="D524" s="3" t="n">
+        <v>5.1144148</v>
+      </c>
+      <c r="E524" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C525" s="2" t="n">
+        <v>1890887686.185818</v>
+      </c>
+      <c r="D525" s="3" t="n">
+        <v>10.96123192</v>
+      </c>
+      <c r="E525" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C526" s="2" t="n">
+        <v>3772820396.145967</v>
+      </c>
+      <c r="D526" s="3" t="n">
+        <v>21.87055299</v>
+      </c>
+      <c r="E526" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C527" s="2" t="n">
+        <v>5837931203.545683</v>
+      </c>
+      <c r="D527" s="3" t="n">
+        <v>33.84173386</v>
+      </c>
+      <c r="E527" t="n">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C528" s="2" t="n">
+        <v>175690866.6797449</v>
+      </c>
+      <c r="D528" s="3" t="n">
+        <v>1.01845728</v>
+      </c>
+      <c r="E528" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C529" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D529" s="3" t="n">
+        <v>0.21005147</v>
+      </c>
+      <c r="E529" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5837931203.545683</v>
+        <v>5855026472.045132</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.84173386</v>
+        <v>33.92279441</v>
       </c>
       <c r="E2" t="n">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3772820396.145967</v>
+        <v>3759023555.223317</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.87055299</v>
+        <v>21.77899346</v>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2431361877.452255</v>
+        <v>2428610482.235768</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.09429106</v>
+        <v>14.07085937</v>
       </c>
       <c r="E4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2223486898.746715</v>
+        <v>2227767008.306568</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.88926663</v>
+        <v>12.90721444</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1890887686.185818</v>
+        <v>1895291894.038332</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.96123192</v>
+        <v>10.98092341</v>
       </c>
       <c r="E6" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882271631.4190582</v>
+        <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.1144148</v>
+        <v>5.11156449</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175690866.6797449</v>
+        <v>175655412.9614999</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01845728</v>
+        <v>1.01771059</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21005147</v>
+        <v>0.20993983</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17250685879.42812</v>
+        <v>17259858965.88143</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E529"/>
+  <dimension ref="A1:E537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11801,6 +11801,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C530" s="2" t="n">
+        <v>2227767008.306568</v>
+      </c>
+      <c r="D530" s="3" t="n">
+        <v>12.90721444</v>
+      </c>
+      <c r="E530" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C531" s="2" t="n">
+        <v>2428610482.235768</v>
+      </c>
+      <c r="D531" s="3" t="n">
+        <v>14.07085937</v>
+      </c>
+      <c r="E531" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C532" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D532" s="3" t="n">
+        <v>5.11156449</v>
+      </c>
+      <c r="E532" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C533" s="2" t="n">
+        <v>1895291894.038332</v>
+      </c>
+      <c r="D533" s="3" t="n">
+        <v>10.98092341</v>
+      </c>
+      <c r="E533" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C534" s="2" t="n">
+        <v>3759023555.223317</v>
+      </c>
+      <c r="D534" s="3" t="n">
+        <v>21.77899346</v>
+      </c>
+      <c r="E534" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C535" s="2" t="n">
+        <v>5855026472.045132</v>
+      </c>
+      <c r="D535" s="3" t="n">
+        <v>33.92279441</v>
+      </c>
+      <c r="E535" t="n">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C536" s="2" t="n">
+        <v>175655412.9614999</v>
+      </c>
+      <c r="D536" s="3" t="n">
+        <v>1.01771059</v>
+      </c>
+      <c r="E536" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C537" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D537" s="3" t="n">
+        <v>0.20993983</v>
+      </c>
+      <c r="E537" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
